--- a/research/traditional_assets/database/data/spain/spain_packaging_container.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_packaging_container.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08568260228261644</v>
+        <v>0.0855021457769099</v>
       </c>
       <c r="C2">
-        <v>3723.749565332773</v>
+        <v>3702.389800910524</v>
       </c>
       <c r="D2">
-        <v>3652.649565332773</v>
+        <v>3669.251800910524</v>
       </c>
       <c r="E2">
-        <v>-583.4</v>
+        <v>-545.438</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>37.962</v>
       </c>
       <c r="G2">
         <v>71.09999999999999</v>
@@ -1451,28 +1451,28 @@
         <v>306.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.9094886</v>
       </c>
       <c r="N2">
-        <v>306.6</v>
+        <v>304.6905114</v>
       </c>
       <c r="O2">
-        <v>76.64999999999999</v>
+        <v>76.17262785</v>
       </c>
       <c r="P2">
-        <v>229.95</v>
+        <v>228.51788355</v>
       </c>
       <c r="Q2">
-        <v>350.25</v>
+        <v>348.81788355</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08568260228261644</v>
+        <v>0.0859847432089999</v>
       </c>
       <c r="T2">
-        <v>0.6169711731246059</v>
+        <v>0.6216451971634287</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>160.5665516934744</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0855021457769099</v>
+        <v>0.08532168927120337</v>
       </c>
       <c r="C3">
-        <v>3702.389800910524</v>
+        <v>3681.18164850054</v>
       </c>
       <c r="D3">
-        <v>3669.251800910524</v>
+        <v>3686.00564850054</v>
       </c>
       <c r="E3">
-        <v>-545.438</v>
+        <v>-507.476</v>
       </c>
       <c r="F3">
-        <v>37.962</v>
+        <v>75.92400000000001</v>
       </c>
       <c r="G3">
         <v>71.09999999999999</v>
@@ -1533,28 +1533,28 @@
         <v>306.6</v>
       </c>
       <c r="M3">
-        <v>1.9094886</v>
+        <v>3.8189772</v>
       </c>
       <c r="N3">
-        <v>304.6905114</v>
+        <v>302.7810228</v>
       </c>
       <c r="O3">
-        <v>76.17262785</v>
+        <v>75.69525569999999</v>
       </c>
       <c r="P3">
-        <v>228.51788355</v>
+        <v>227.0857671</v>
       </c>
       <c r="Q3">
-        <v>348.81788355</v>
+        <v>347.3857671</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0859847432089999</v>
+        <v>0.08629305027673813</v>
       </c>
       <c r="T3">
-        <v>0.6216451971634287</v>
+        <v>0.6264146094479418</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>160.5665516934744</v>
+        <v>80.28327584673717</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08532168927120337</v>
+        <v>0.08514123276549682</v>
       </c>
       <c r="C4">
-        <v>3681.18164850054</v>
+        <v>3660.127194415735</v>
       </c>
       <c r="D4">
-        <v>3686.00564850054</v>
+        <v>3702.913194415735</v>
       </c>
       <c r="E4">
-        <v>-507.476</v>
+        <v>-469.514</v>
       </c>
       <c r="F4">
-        <v>75.92400000000001</v>
+        <v>113.886</v>
       </c>
       <c r="G4">
         <v>71.09999999999999</v>
@@ -1615,28 +1615,28 @@
         <v>306.6</v>
       </c>
       <c r="M4">
-        <v>3.8189772</v>
+        <v>5.7284658</v>
       </c>
       <c r="N4">
-        <v>302.7810228</v>
+        <v>300.8715342</v>
       </c>
       <c r="O4">
-        <v>75.69525569999999</v>
+        <v>75.21788355</v>
       </c>
       <c r="P4">
-        <v>227.0857671</v>
+        <v>225.65365065</v>
       </c>
       <c r="Q4">
-        <v>347.3857671</v>
+        <v>345.95365065</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08629305027673813</v>
+        <v>0.08660771419123384</v>
       </c>
       <c r="T4">
-        <v>0.6264146094479418</v>
+        <v>0.6312823601300735</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>80.28327584673717</v>
+        <v>53.52218389782478</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08514123276549682</v>
+        <v>0.08496077625979027</v>
       </c>
       <c r="C5">
-        <v>3660.127194415735</v>
+        <v>3639.228563424716</v>
       </c>
       <c r="D5">
-        <v>3702.913194415735</v>
+        <v>3719.976563424716</v>
       </c>
       <c r="E5">
-        <v>-469.514</v>
+        <v>-431.552</v>
       </c>
       <c r="F5">
-        <v>113.886</v>
+        <v>151.848</v>
       </c>
       <c r="G5">
         <v>71.09999999999999</v>
@@ -1697,28 +1697,28 @@
         <v>306.6</v>
       </c>
       <c r="M5">
-        <v>5.7284658</v>
+        <v>7.6379544</v>
       </c>
       <c r="N5">
-        <v>300.8715342</v>
+        <v>298.9620456</v>
       </c>
       <c r="O5">
-        <v>75.21788355</v>
+        <v>74.74051139999999</v>
       </c>
       <c r="P5">
-        <v>225.65365065</v>
+        <v>224.2215342</v>
       </c>
       <c r="Q5">
-        <v>345.95365065</v>
+        <v>344.5215342</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08660771419123384</v>
+        <v>0.08692893360394821</v>
       </c>
       <c r="T5">
-        <v>0.6312823601300735</v>
+        <v>0.6362515222847499</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>53.52218389782478</v>
+        <v>40.14163792336858</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08496077625979027</v>
+        <v>0.08478031975408373</v>
       </c>
       <c r="C6">
-        <v>3639.228563424716</v>
+        <v>3618.487919641926</v>
       </c>
       <c r="D6">
-        <v>3719.976563424716</v>
+        <v>3737.197919641926</v>
       </c>
       <c r="E6">
-        <v>-431.552</v>
+        <v>-393.5899999999999</v>
       </c>
       <c r="F6">
-        <v>151.848</v>
+        <v>189.81</v>
       </c>
       <c r="G6">
         <v>71.09999999999999</v>
@@ -1779,28 +1779,28 @@
         <v>306.6</v>
       </c>
       <c r="M6">
-        <v>7.6379544</v>
+        <v>9.547443000000001</v>
       </c>
       <c r="N6">
-        <v>298.9620456</v>
+        <v>297.052557</v>
       </c>
       <c r="O6">
-        <v>74.74051139999999</v>
+        <v>74.26313924999999</v>
       </c>
       <c r="P6">
-        <v>224.2215342</v>
+        <v>222.78941775</v>
       </c>
       <c r="Q6">
-        <v>344.5215342</v>
+        <v>343.08941775</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08692893360394821</v>
+        <v>0.08725691553061446</v>
       </c>
       <c r="T6">
-        <v>0.6362515222847499</v>
+        <v>0.6413252983795246</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>40.14163792336858</v>
+        <v>32.11331033869487</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08478031975408373</v>
+        <v>0.08459986324837718</v>
       </c>
       <c r="C7">
-        <v>3618.487919641926</v>
+        <v>3597.907467442629</v>
       </c>
       <c r="D7">
-        <v>3737.197919641926</v>
+        <v>3754.579467442629</v>
       </c>
       <c r="E7">
-        <v>-393.5899999999999</v>
+        <v>-355.6279999999999</v>
       </c>
       <c r="F7">
-        <v>189.81</v>
+        <v>227.772</v>
       </c>
       <c r="G7">
         <v>71.09999999999999</v>
@@ -1861,28 +1861,28 @@
         <v>306.6</v>
       </c>
       <c r="M7">
-        <v>9.547443000000001</v>
+        <v>11.4569316</v>
       </c>
       <c r="N7">
-        <v>297.052557</v>
+        <v>295.1430683999999</v>
       </c>
       <c r="O7">
-        <v>74.26313924999999</v>
+        <v>73.78576709999999</v>
       </c>
       <c r="P7">
-        <v>222.78941775</v>
+        <v>221.3573013</v>
       </c>
       <c r="Q7">
-        <v>343.08941775</v>
+        <v>341.6573013</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08725691553061446</v>
+        <v>0.08759187579614594</v>
       </c>
       <c r="T7">
-        <v>0.6413252983795246</v>
+        <v>0.6465070271571668</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>32.11331033869487</v>
+        <v>26.76109194891238</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08459986324837718</v>
+        <v>0.08441940674267066</v>
       </c>
       <c r="C8">
-        <v>3597.907467442629</v>
+        <v>3577.489452403524</v>
       </c>
       <c r="D8">
-        <v>3754.579467442629</v>
+        <v>3772.123452403524</v>
       </c>
       <c r="E8">
-        <v>-355.6279999999999</v>
+        <v>-317.666</v>
       </c>
       <c r="F8">
-        <v>227.772</v>
+        <v>265.734</v>
       </c>
       <c r="G8">
         <v>71.09999999999999</v>
@@ -1943,28 +1943,28 @@
         <v>306.6</v>
       </c>
       <c r="M8">
-        <v>11.4569316</v>
+        <v>13.3664202</v>
       </c>
       <c r="N8">
-        <v>295.1430683999999</v>
+        <v>293.2335798</v>
       </c>
       <c r="O8">
-        <v>73.78576709999999</v>
+        <v>73.30839494999999</v>
       </c>
       <c r="P8">
-        <v>221.3573013</v>
+        <v>219.92518485</v>
       </c>
       <c r="Q8">
-        <v>341.6573013</v>
+        <v>340.22518485</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08759187579614594</v>
+        <v>0.08793403950824802</v>
       </c>
       <c r="T8">
-        <v>0.6465070271571668</v>
+        <v>0.6518001909622853</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>26.76109194891239</v>
+        <v>22.93807881335348</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08441940674267065</v>
+        <v>0.08423895023696412</v>
       </c>
       <c r="C9">
-        <v>3577.489452403525</v>
+        <v>3557.2361622699</v>
       </c>
       <c r="D9">
-        <v>3772.123452403525</v>
+        <v>3789.8321622699</v>
       </c>
       <c r="E9">
-        <v>-317.6659999999999</v>
+        <v>-279.704</v>
       </c>
       <c r="F9">
-        <v>265.734</v>
+        <v>303.696</v>
       </c>
       <c r="G9">
         <v>71.09999999999999</v>
@@ -2025,28 +2025,28 @@
         <v>306.6</v>
       </c>
       <c r="M9">
-        <v>13.3664202</v>
+        <v>15.2759088</v>
       </c>
       <c r="N9">
-        <v>293.2335798</v>
+        <v>291.3240911999999</v>
       </c>
       <c r="O9">
-        <v>73.30839494999999</v>
+        <v>72.83102279999999</v>
       </c>
       <c r="P9">
-        <v>219.92518485</v>
+        <v>218.4930684</v>
       </c>
       <c r="Q9">
-        <v>340.22518485</v>
+        <v>338.7930684</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08793403950824802</v>
+        <v>0.08828364156191751</v>
       </c>
       <c r="T9">
-        <v>0.6518001909622853</v>
+        <v>0.6572084235457759</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.93807881335347</v>
+        <v>20.07081896168429</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08423895023696412</v>
+        <v>0.08405849373125758</v>
       </c>
       <c r="C10">
-        <v>3557.2361622699</v>
+        <v>3537.149927950104</v>
       </c>
       <c r="D10">
-        <v>3789.8321622699</v>
+        <v>3807.707927950104</v>
       </c>
       <c r="E10">
-        <v>-279.704</v>
+        <v>-241.742</v>
       </c>
       <c r="F10">
-        <v>303.696</v>
+        <v>341.658</v>
       </c>
       <c r="G10">
         <v>71.09999999999999</v>
@@ -2107,28 +2107,28 @@
         <v>306.6</v>
       </c>
       <c r="M10">
-        <v>15.2759088</v>
+        <v>17.1853974</v>
       </c>
       <c r="N10">
-        <v>291.3240911999999</v>
+        <v>289.4146026</v>
       </c>
       <c r="O10">
-        <v>72.83102279999999</v>
+        <v>72.35365064999999</v>
       </c>
       <c r="P10">
-        <v>218.4930684</v>
+        <v>217.06095195</v>
       </c>
       <c r="Q10">
-        <v>338.7930684</v>
+        <v>337.36095195</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08828364156191751</v>
+        <v>0.08864092717720612</v>
       </c>
       <c r="T10">
-        <v>0.6572084235457759</v>
+        <v>0.6627355183838486</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.07081896168429</v>
+        <v>17.8407279659416</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08405849373125758</v>
+        <v>0.08387803722555102</v>
       </c>
       <c r="C11">
-        <v>3537.149927950104</v>
+        <v>3517.233124538333</v>
       </c>
       <c r="D11">
-        <v>3807.707927950104</v>
+        <v>3825.753124538333</v>
       </c>
       <c r="E11">
-        <v>-241.742</v>
+        <v>-203.78</v>
       </c>
       <c r="F11">
-        <v>341.658</v>
+        <v>379.62</v>
       </c>
       <c r="G11">
         <v>71.09999999999999</v>
@@ -2189,28 +2189,28 @@
         <v>306.6</v>
       </c>
       <c r="M11">
-        <v>17.1853974</v>
+        <v>19.094886</v>
       </c>
       <c r="N11">
-        <v>289.4146026</v>
+        <v>287.505114</v>
       </c>
       <c r="O11">
-        <v>72.35365064999999</v>
+        <v>71.8762785</v>
       </c>
       <c r="P11">
-        <v>217.06095195</v>
+        <v>215.6288355</v>
       </c>
       <c r="Q11">
-        <v>337.36095195</v>
+        <v>335.9288355</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08864092717720612</v>
+        <v>0.08900615247283447</v>
       </c>
       <c r="T11">
-        <v>0.6627355183838486</v>
+        <v>0.6683854375516564</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.8407279659416</v>
+        <v>16.05665516934744</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08387803722555102</v>
+        <v>0.08369758071984448</v>
       </c>
       <c r="C12">
-        <v>3517.233124538333</v>
+        <v>3497.488172366629</v>
       </c>
       <c r="D12">
-        <v>3825.753124538333</v>
+        <v>3843.970172366629</v>
       </c>
       <c r="E12">
-        <v>-203.7799999999999</v>
+        <v>-165.8179999999999</v>
       </c>
       <c r="F12">
-        <v>379.6200000000001</v>
+        <v>417.5820000000001</v>
       </c>
       <c r="G12">
         <v>71.09999999999999</v>
@@ -2271,28 +2271,28 @@
         <v>306.6</v>
       </c>
       <c r="M12">
-        <v>19.094886</v>
+        <v>21.0043746</v>
       </c>
       <c r="N12">
-        <v>287.5051139999999</v>
+        <v>285.5956254</v>
       </c>
       <c r="O12">
-        <v>71.87627849999998</v>
+        <v>71.39890634999999</v>
       </c>
       <c r="P12">
-        <v>215.6288355</v>
+        <v>214.19671905</v>
       </c>
       <c r="Q12">
-        <v>335.9288354999999</v>
+        <v>334.49671905</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08900615247283447</v>
+        <v>0.08937958507847696</v>
       </c>
       <c r="T12">
-        <v>0.6683854375516564</v>
+        <v>0.6741623211951453</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.05665516934743</v>
+        <v>14.5969592448613</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08369758071984448</v>
+        <v>0.08351712421413796</v>
       </c>
       <c r="C13">
-        <v>3497.488172366629</v>
+        <v>3477.917538087067</v>
       </c>
       <c r="D13">
-        <v>3843.970172366629</v>
+        <v>3862.361538087066</v>
       </c>
       <c r="E13">
-        <v>-165.8179999999999</v>
+        <v>-127.8559999999999</v>
       </c>
       <c r="F13">
-        <v>417.5820000000001</v>
+        <v>455.544</v>
       </c>
       <c r="G13">
         <v>71.09999999999999</v>
@@ -2353,28 +2353,28 @@
         <v>306.6</v>
       </c>
       <c r="M13">
-        <v>21.0043746</v>
+        <v>22.9138632</v>
       </c>
       <c r="N13">
-        <v>285.5956254</v>
+        <v>283.6861368</v>
       </c>
       <c r="O13">
-        <v>71.39890634999999</v>
+        <v>70.9215342</v>
       </c>
       <c r="P13">
-        <v>214.19671905</v>
+        <v>212.7646026</v>
       </c>
       <c r="Q13">
-        <v>334.49671905</v>
+        <v>333.0646026</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08937958507847696</v>
+        <v>0.08976150478879312</v>
       </c>
       <c r="T13">
-        <v>0.6741623211951453</v>
+        <v>0.6800704976487133</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.5969592448613</v>
+        <v>13.3805459744562</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08351712421413796</v>
+        <v>0.08348291770843141</v>
       </c>
       <c r="C14">
-        <v>3477.917538087067</v>
+        <v>3443.461580082422</v>
       </c>
       <c r="D14">
-        <v>3862.361538087066</v>
+        <v>3865.867580082422</v>
       </c>
       <c r="E14">
-        <v>-127.8559999999999</v>
+        <v>-89.89399999999995</v>
       </c>
       <c r="F14">
-        <v>455.544</v>
+        <v>493.506</v>
       </c>
       <c r="G14">
         <v>71.09999999999999</v>
@@ -2435,45 +2435,45 @@
         <v>306.6</v>
       </c>
       <c r="M14">
-        <v>22.9138632</v>
+        <v>25.5636108</v>
       </c>
       <c r="N14">
-        <v>283.6861368</v>
+        <v>281.0363892</v>
       </c>
       <c r="O14">
-        <v>70.9215342</v>
+        <v>70.25909729999999</v>
       </c>
       <c r="P14">
-        <v>212.7646026</v>
+        <v>210.7772919</v>
       </c>
       <c r="Q14">
-        <v>333.0646026</v>
+        <v>331.0772919</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08976150478879312</v>
+        <v>0.09015220426256484</v>
       </c>
       <c r="T14">
-        <v>0.6800704976487133</v>
+        <v>0.6861144942506393</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.3805459744562</v>
+        <v>11.99361085563077</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08348291770843141</v>
+        <v>0.08331371120272486</v>
       </c>
       <c r="C15">
-        <v>3443.461580082422</v>
+        <v>3422.936669716531</v>
       </c>
       <c r="D15">
-        <v>3865.867580082422</v>
+        <v>3883.304669716531</v>
       </c>
       <c r="E15">
-        <v>-89.89399999999995</v>
+        <v>-51.9319999999999</v>
       </c>
       <c r="F15">
-        <v>493.506</v>
+        <v>531.4680000000001</v>
       </c>
       <c r="G15">
         <v>71.09999999999999</v>
@@ -2517,28 +2517,28 @@
         <v>306.6</v>
       </c>
       <c r="M15">
-        <v>25.5636108</v>
+        <v>27.5300424</v>
       </c>
       <c r="N15">
-        <v>281.0363892</v>
+        <v>279.0699576</v>
       </c>
       <c r="O15">
-        <v>70.25909729999999</v>
+        <v>69.76748939999999</v>
       </c>
       <c r="P15">
-        <v>210.7772919</v>
+        <v>209.3024682</v>
       </c>
       <c r="Q15">
-        <v>331.0772919</v>
+        <v>329.6024682</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09015220426256484</v>
+        <v>0.09055198977061031</v>
       </c>
       <c r="T15">
-        <v>0.6861144942506393</v>
+        <v>0.6922990489130753</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.99361085563077</v>
+        <v>11.13692436594286</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08331371120272486</v>
+        <v>0.08314450469701831</v>
       </c>
       <c r="C16">
-        <v>3422.936669716531</v>
+        <v>3402.56977290742</v>
       </c>
       <c r="D16">
-        <v>3883.304669716531</v>
+        <v>3900.89977290742</v>
       </c>
       <c r="E16">
-        <v>-51.9319999999999</v>
+        <v>-13.9699999999998</v>
       </c>
       <c r="F16">
-        <v>531.4680000000001</v>
+        <v>569.4300000000002</v>
       </c>
       <c r="G16">
         <v>71.09999999999999</v>
@@ -2599,28 +2599,28 @@
         <v>306.6</v>
       </c>
       <c r="M16">
-        <v>27.5300424</v>
+        <v>29.49647400000001</v>
       </c>
       <c r="N16">
-        <v>279.0699576</v>
+        <v>277.1035259999999</v>
       </c>
       <c r="O16">
-        <v>69.76748939999999</v>
+        <v>69.27588149999998</v>
       </c>
       <c r="P16">
-        <v>209.3024682</v>
+        <v>207.8276445</v>
       </c>
       <c r="Q16">
-        <v>329.6024682</v>
+        <v>328.1276445</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09055198977061031</v>
+        <v>0.09096118199649214</v>
       </c>
       <c r="T16">
-        <v>0.6922990489130753</v>
+        <v>0.6986291225087449</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.13692436594286</v>
+        <v>10.39446274154666</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08314450469701831</v>
+        <v>0.08317929819131177</v>
       </c>
       <c r="C17">
-        <v>3402.56977290742</v>
+        <v>3360.976727367362</v>
       </c>
       <c r="D17">
-        <v>3900.89977290742</v>
+        <v>3897.268727367363</v>
       </c>
       <c r="E17">
-        <v>-13.96999999999991</v>
+        <v>23.99200000000008</v>
       </c>
       <c r="F17">
-        <v>569.4300000000001</v>
+        <v>607.3920000000001</v>
       </c>
       <c r="G17">
         <v>71.09999999999999</v>
@@ -2681,45 +2681,45 @@
         <v>306.6</v>
       </c>
       <c r="M17">
-        <v>29.496474</v>
+        <v>32.495472</v>
       </c>
       <c r="N17">
-        <v>277.103526</v>
+        <v>274.104528</v>
       </c>
       <c r="O17">
-        <v>69.2758815</v>
+        <v>68.52613199999999</v>
       </c>
       <c r="P17">
-        <v>207.8276445</v>
+        <v>205.578396</v>
       </c>
       <c r="Q17">
-        <v>328.1276445</v>
+        <v>325.878396</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09096118199649214</v>
+        <v>0.09138011689441879</v>
       </c>
       <c r="T17">
-        <v>0.6986291225087449</v>
+        <v>0.7051099121424067</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>10.39446274154667</v>
+        <v>9.435160689464672</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08317929819131177</v>
+        <v>0.08302284168560524</v>
       </c>
       <c r="C18">
-        <v>3360.976727367362</v>
+        <v>3339.395879887458</v>
       </c>
       <c r="D18">
-        <v>3897.268727367363</v>
+        <v>3913.649879887458</v>
       </c>
       <c r="E18">
-        <v>23.99200000000008</v>
+        <v>61.95400000000006</v>
       </c>
       <c r="F18">
-        <v>607.3920000000001</v>
+        <v>645.354</v>
       </c>
       <c r="G18">
         <v>71.09999999999999</v>
@@ -2763,28 +2763,28 @@
         <v>306.6</v>
       </c>
       <c r="M18">
-        <v>32.495472</v>
+        <v>34.526439</v>
       </c>
       <c r="N18">
-        <v>274.104528</v>
+        <v>272.073561</v>
       </c>
       <c r="O18">
-        <v>68.52613199999999</v>
+        <v>68.01839025</v>
       </c>
       <c r="P18">
-        <v>205.578396</v>
+        <v>204.05517075</v>
       </c>
       <c r="Q18">
-        <v>325.878396</v>
+        <v>324.35517075</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09138011689441879</v>
+        <v>0.09180914660916295</v>
       </c>
       <c r="T18">
-        <v>0.7051099121424067</v>
+        <v>0.7117468653816991</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.435160689464672</v>
+        <v>8.88015123714322</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08302284168560524</v>
+        <v>0.08286638517989869</v>
       </c>
       <c r="C19">
-        <v>3339.395879887458</v>
+        <v>3317.953321472986</v>
       </c>
       <c r="D19">
-        <v>3913.649879887458</v>
+        <v>3930.169321472987</v>
       </c>
       <c r="E19">
-        <v>61.95400000000006</v>
+        <v>99.91600000000017</v>
       </c>
       <c r="F19">
-        <v>645.354</v>
+        <v>683.3160000000001</v>
       </c>
       <c r="G19">
         <v>71.09999999999999</v>
@@ -2845,28 +2845,28 @@
         <v>306.6</v>
       </c>
       <c r="M19">
-        <v>34.526439</v>
+        <v>36.55740600000001</v>
       </c>
       <c r="N19">
-        <v>272.073561</v>
+        <v>270.042594</v>
       </c>
       <c r="O19">
-        <v>68.01839025</v>
+        <v>67.51064849999999</v>
       </c>
       <c r="P19">
-        <v>204.05517075</v>
+        <v>202.5319454999999</v>
       </c>
       <c r="Q19">
-        <v>324.35517075</v>
+        <v>322.8319455</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09180914660916295</v>
+        <v>0.09224864046329109</v>
       </c>
       <c r="T19">
-        <v>0.7117468653816991</v>
+        <v>0.7185456955292666</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.88015123714322</v>
+        <v>8.386809501746374</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08286638517989869</v>
+        <v>0.08270992867419216</v>
       </c>
       <c r="C20">
-        <v>3317.953321472986</v>
+        <v>3296.650810693366</v>
       </c>
       <c r="D20">
-        <v>3930.169321472987</v>
+        <v>3946.828810693366</v>
       </c>
       <c r="E20">
-        <v>99.91600000000005</v>
+        <v>137.878</v>
       </c>
       <c r="F20">
-        <v>683.316</v>
+        <v>721.278</v>
       </c>
       <c r="G20">
         <v>71.09999999999999</v>
@@ -2927,28 +2927,28 @@
         <v>306.6</v>
       </c>
       <c r="M20">
-        <v>36.557406</v>
+        <v>38.588373</v>
       </c>
       <c r="N20">
-        <v>270.042594</v>
+        <v>268.011627</v>
       </c>
       <c r="O20">
-        <v>67.51064849999999</v>
+        <v>67.00290674999999</v>
       </c>
       <c r="P20">
-        <v>202.5319454999999</v>
+        <v>201.00872025</v>
       </c>
       <c r="Q20">
-        <v>322.8319455</v>
+        <v>321.30872025</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09224864046329109</v>
+        <v>0.09269898601752119</v>
       </c>
       <c r="T20">
-        <v>0.7185456955292666</v>
+        <v>0.7255123980261571</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.386809501746376</v>
+        <v>7.945398475338672</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08270992867419216</v>
+        <v>0.08267347216848561</v>
       </c>
       <c r="C21">
-        <v>3296.650810693366</v>
+        <v>3262.591008631286</v>
       </c>
       <c r="D21">
-        <v>3946.828810693366</v>
+        <v>3950.731008631286</v>
       </c>
       <c r="E21">
-        <v>137.878</v>
+        <v>175.8400000000001</v>
       </c>
       <c r="F21">
-        <v>721.278</v>
+        <v>759.2400000000001</v>
       </c>
       <c r="G21">
         <v>71.09999999999999</v>
@@ -3009,45 +3009,45 @@
         <v>306.6</v>
       </c>
       <c r="M21">
-        <v>38.588373</v>
+        <v>41.22673200000001</v>
       </c>
       <c r="N21">
-        <v>268.011627</v>
+        <v>265.3732679999999</v>
       </c>
       <c r="O21">
-        <v>67.00290674999999</v>
+        <v>66.34331699999998</v>
       </c>
       <c r="P21">
-        <v>201.00872025</v>
+        <v>199.029951</v>
       </c>
       <c r="Q21">
-        <v>321.30872025</v>
+        <v>319.3299509999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09269898601752119</v>
+        <v>0.09316059021060702</v>
       </c>
       <c r="T21">
-        <v>0.7255123980261571</v>
+        <v>0.7326532680854695</v>
       </c>
       <c r="U21">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>7.945398475338672</v>
+        <v>7.436922237736425</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08267347216848561</v>
+        <v>0.08252301566277909</v>
       </c>
       <c r="C22">
-        <v>3262.591008631286</v>
+        <v>3240.815402145464</v>
       </c>
       <c r="D22">
-        <v>3950.731008631286</v>
+        <v>3966.917402145464</v>
       </c>
       <c r="E22">
-        <v>175.8400000000001</v>
+        <v>213.8020000000001</v>
       </c>
       <c r="F22">
-        <v>759.2400000000001</v>
+        <v>797.2020000000001</v>
       </c>
       <c r="G22">
         <v>71.09999999999999</v>
@@ -3091,28 +3091,28 @@
         <v>306.6</v>
       </c>
       <c r="M22">
-        <v>41.22673200000001</v>
+        <v>43.28806860000001</v>
       </c>
       <c r="N22">
-        <v>265.3732679999999</v>
+        <v>263.3119313999999</v>
       </c>
       <c r="O22">
-        <v>66.34331699999998</v>
+        <v>65.82798284999998</v>
       </c>
       <c r="P22">
-        <v>199.029951</v>
+        <v>197.48394855</v>
       </c>
       <c r="Q22">
-        <v>319.3299509999999</v>
+        <v>317.7839485499999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09316059021060702</v>
+        <v>0.0936338805857963</v>
       </c>
       <c r="T22">
-        <v>0.7326532680854695</v>
+        <v>0.739974919665271</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.436922237736425</v>
+        <v>7.0827830835585</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08252301566277909</v>
+        <v>0.08237255915707253</v>
       </c>
       <c r="C23">
-        <v>3240.815402145464</v>
+        <v>3219.172974647622</v>
       </c>
       <c r="D23">
-        <v>3966.917402145464</v>
+        <v>3983.236974647622</v>
       </c>
       <c r="E23">
-        <v>213.802</v>
+        <v>251.7640000000001</v>
       </c>
       <c r="F23">
-        <v>797.202</v>
+        <v>835.1640000000001</v>
       </c>
       <c r="G23">
         <v>71.09999999999999</v>
@@ -3173,28 +3173,28 @@
         <v>306.6</v>
       </c>
       <c r="M23">
-        <v>43.2880686</v>
+        <v>45.34940520000001</v>
       </c>
       <c r="N23">
-        <v>263.3119313999999</v>
+        <v>261.2505947999999</v>
       </c>
       <c r="O23">
-        <v>65.82798284999998</v>
+        <v>65.31264869999998</v>
       </c>
       <c r="P23">
-        <v>197.48394855</v>
+        <v>195.9379460999999</v>
       </c>
       <c r="Q23">
-        <v>317.7839485499999</v>
+        <v>316.2379460999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0936338805857963</v>
+        <v>0.09411930661163145</v>
       </c>
       <c r="T23">
-        <v>0.739974919665271</v>
+        <v>0.7474843059009648</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.082783083558501</v>
+        <v>6.760838397942205</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08237255915707253</v>
+        <v>0.08222210265136601</v>
       </c>
       <c r="C24">
-        <v>3219.172974647622</v>
+        <v>3197.665376589846</v>
       </c>
       <c r="D24">
-        <v>3983.236974647622</v>
+        <v>3999.691376589846</v>
       </c>
       <c r="E24">
-        <v>251.7640000000001</v>
+        <v>289.7260000000001</v>
       </c>
       <c r="F24">
-        <v>835.1640000000001</v>
+        <v>873.1260000000001</v>
       </c>
       <c r="G24">
         <v>71.09999999999999</v>
@@ -3255,28 +3255,28 @@
         <v>306.6</v>
       </c>
       <c r="M24">
-        <v>45.34940520000001</v>
+        <v>47.4107418</v>
       </c>
       <c r="N24">
-        <v>261.2505947999999</v>
+        <v>259.1892582</v>
       </c>
       <c r="O24">
-        <v>65.31264869999998</v>
+        <v>64.79731455</v>
       </c>
       <c r="P24">
-        <v>195.9379460999999</v>
+        <v>194.39194365</v>
       </c>
       <c r="Q24">
-        <v>316.2379460999999</v>
+        <v>314.69194365</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09411930661163145</v>
+        <v>0.09461734110567013</v>
       </c>
       <c r="T24">
-        <v>0.7474843059009648</v>
+        <v>0.7551887411297936</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.760838397942205</v>
+        <v>6.466888902379502</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08222210265136601</v>
+        <v>0.08207164614565947</v>
       </c>
       <c r="C25">
-        <v>3197.665376589846</v>
+        <v>3176.294285808845</v>
       </c>
       <c r="D25">
-        <v>3999.691376589846</v>
+        <v>4016.282285808845</v>
       </c>
       <c r="E25">
-        <v>289.7260000000001</v>
+        <v>327.6880000000002</v>
       </c>
       <c r="F25">
-        <v>873.1260000000001</v>
+        <v>911.0880000000002</v>
       </c>
       <c r="G25">
         <v>71.09999999999999</v>
@@ -3337,28 +3337,28 @@
         <v>306.6</v>
       </c>
       <c r="M25">
-        <v>47.4107418</v>
+        <v>49.47207840000001</v>
       </c>
       <c r="N25">
-        <v>259.1892582</v>
+        <v>257.1279216</v>
       </c>
       <c r="O25">
-        <v>64.79731455</v>
+        <v>64.28198039999999</v>
       </c>
       <c r="P25">
-        <v>194.39194365</v>
+        <v>192.8459412</v>
       </c>
       <c r="Q25">
-        <v>314.69194365</v>
+        <v>313.1459412</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09461734110567013</v>
+        <v>0.09512848177060455</v>
       </c>
       <c r="T25">
-        <v>0.7551887411297936</v>
+        <v>0.7630959246541179</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.466888902379502</v>
+        <v>6.197435198113689</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08207164614565947</v>
+        <v>0.08210868963995292</v>
       </c>
       <c r="C26">
-        <v>3176.294285808845</v>
+        <v>3134.234723175476</v>
       </c>
       <c r="D26">
-        <v>4016.282285808845</v>
+        <v>4012.184723175476</v>
       </c>
       <c r="E26">
-        <v>327.6880000000001</v>
+        <v>365.6500000000001</v>
       </c>
       <c r="F26">
-        <v>911.0880000000001</v>
+        <v>949.0500000000001</v>
       </c>
       <c r="G26">
         <v>71.09999999999999</v>
@@ -3419,45 +3419,45 @@
         <v>306.6</v>
       </c>
       <c r="M26">
-        <v>49.47207840000001</v>
+        <v>52.482465</v>
       </c>
       <c r="N26">
-        <v>257.1279216</v>
+        <v>254.117535</v>
       </c>
       <c r="O26">
-        <v>64.28198039999999</v>
+        <v>63.52938374999999</v>
       </c>
       <c r="P26">
-        <v>192.8459412</v>
+        <v>190.58815125</v>
       </c>
       <c r="Q26">
-        <v>313.1459412</v>
+        <v>310.88815125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09512848177060455</v>
+        <v>0.09565325285327056</v>
       </c>
       <c r="T26">
-        <v>0.7630959246541179</v>
+        <v>0.7712139664057573</v>
       </c>
       <c r="U26">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>6.197435198113689</v>
+        <v>5.841951211704709</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08210868963995292</v>
+        <v>0.08196573313424638</v>
       </c>
       <c r="C27">
-        <v>3134.234723175476</v>
+        <v>3112.132153043669</v>
       </c>
       <c r="D27">
-        <v>4012.184723175476</v>
+        <v>4028.044153043669</v>
       </c>
       <c r="E27">
-        <v>365.6500000000001</v>
+        <v>403.6120000000001</v>
       </c>
       <c r="F27">
-        <v>949.0500000000001</v>
+        <v>987.0120000000001</v>
       </c>
       <c r="G27">
         <v>71.09999999999999</v>
@@ -3501,28 +3501,28 @@
         <v>306.6</v>
       </c>
       <c r="M27">
-        <v>52.482465</v>
+        <v>54.5817636</v>
       </c>
       <c r="N27">
-        <v>254.117535</v>
+        <v>252.0182364</v>
       </c>
       <c r="O27">
-        <v>63.52938374999999</v>
+        <v>63.00455909999999</v>
       </c>
       <c r="P27">
-        <v>190.58815125</v>
+        <v>189.0136773</v>
       </c>
       <c r="Q27">
-        <v>310.88815125</v>
+        <v>309.3136773</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09565325285327056</v>
+        <v>0.09619220693817078</v>
       </c>
       <c r="T27">
-        <v>0.7712139664057573</v>
+        <v>0.7795514146912251</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.841951211704709</v>
+        <v>5.617260780485297</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08196573313424638</v>
+        <v>0.08182277662853985</v>
       </c>
       <c r="C28">
-        <v>3112.132153043669</v>
+        <v>3090.155459309442</v>
       </c>
       <c r="D28">
-        <v>4028.044153043669</v>
+        <v>4044.029459309443</v>
       </c>
       <c r="E28">
-        <v>403.6120000000001</v>
+        <v>441.5740000000002</v>
       </c>
       <c r="F28">
-        <v>987.0120000000001</v>
+        <v>1024.974</v>
       </c>
       <c r="G28">
         <v>71.09999999999999</v>
@@ -3583,28 +3583,28 @@
         <v>306.6</v>
       </c>
       <c r="M28">
-        <v>54.5817636</v>
+        <v>56.68106220000001</v>
       </c>
       <c r="N28">
-        <v>252.0182364</v>
+        <v>249.9189378</v>
       </c>
       <c r="O28">
-        <v>63.00455909999999</v>
+        <v>62.47973444999999</v>
       </c>
       <c r="P28">
-        <v>189.0136773</v>
+        <v>187.43920335</v>
       </c>
       <c r="Q28">
-        <v>309.3136773</v>
+        <v>307.73920335</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09619220693817078</v>
+        <v>0.09674592688841074</v>
       </c>
       <c r="T28">
-        <v>0.7795514146912251</v>
+        <v>0.7881172862173905</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.617260780485297</v>
+        <v>5.409214084911766</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08182277662853985</v>
+        <v>0.08167982012283329</v>
       </c>
       <c r="C29">
-        <v>3090.155459309442</v>
+        <v>3068.30614656646</v>
       </c>
       <c r="D29">
-        <v>4044.029459309443</v>
+        <v>4060.14214656646</v>
       </c>
       <c r="E29">
-        <v>441.5740000000002</v>
+        <v>479.5360000000002</v>
       </c>
       <c r="F29">
-        <v>1024.974</v>
+        <v>1062.936</v>
       </c>
       <c r="G29">
         <v>71.09999999999999</v>
@@ -3665,28 +3665,28 @@
         <v>306.6</v>
       </c>
       <c r="M29">
-        <v>56.68106220000001</v>
+        <v>58.78036080000001</v>
       </c>
       <c r="N29">
-        <v>249.9189378</v>
+        <v>247.8196392</v>
       </c>
       <c r="O29">
-        <v>62.47973444999999</v>
+        <v>61.95490979999999</v>
       </c>
       <c r="P29">
-        <v>187.43920335</v>
+        <v>185.8647294</v>
       </c>
       <c r="Q29">
-        <v>307.73920335</v>
+        <v>306.1647293999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09674592688841074</v>
+        <v>0.09731502794837957</v>
       </c>
       <c r="T29">
-        <v>0.7881172862173905</v>
+        <v>0.7969210986192827</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.409214084911766</v>
+        <v>5.216027867593489</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08167982012283329</v>
+        <v>0.08153686361712675</v>
       </c>
       <c r="C30">
-        <v>3068.30614656646</v>
+        <v>3046.585743483399</v>
       </c>
       <c r="D30">
-        <v>4060.14214656646</v>
+        <v>4076.383743483399</v>
       </c>
       <c r="E30">
-        <v>479.5360000000002</v>
+        <v>517.4980000000002</v>
       </c>
       <c r="F30">
-        <v>1062.936</v>
+        <v>1100.898</v>
       </c>
       <c r="G30">
         <v>71.09999999999999</v>
@@ -3747,28 +3747,28 @@
         <v>306.6</v>
       </c>
       <c r="M30">
-        <v>58.78036080000001</v>
+        <v>60.87965940000001</v>
       </c>
       <c r="N30">
-        <v>247.8196392</v>
+        <v>245.7203406</v>
       </c>
       <c r="O30">
-        <v>61.95490979999999</v>
+        <v>61.43008514999999</v>
       </c>
       <c r="P30">
-        <v>185.8647294</v>
+        <v>184.29025545</v>
       </c>
       <c r="Q30">
-        <v>306.1647293999999</v>
+        <v>304.59025545</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09731502794837957</v>
+        <v>0.09790016002412219</v>
       </c>
       <c r="T30">
-        <v>0.7969210986192827</v>
+        <v>0.8059729057367211</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.216027867593489</v>
+        <v>5.036164837676472</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08153686361712675</v>
+        <v>0.08139390711142021</v>
       </c>
       <c r="C31">
-        <v>3046.585743483399</v>
+        <v>3024.995803287431</v>
       </c>
       <c r="D31">
-        <v>4076.383743483399</v>
+        <v>4092.75580328743</v>
       </c>
       <c r="E31">
-        <v>517.4979999999999</v>
+        <v>555.4600000000002</v>
       </c>
       <c r="F31">
-        <v>1100.898</v>
+        <v>1138.86</v>
       </c>
       <c r="G31">
         <v>71.09999999999999</v>
@@ -3829,28 +3829,28 @@
         <v>306.6</v>
       </c>
       <c r="M31">
-        <v>60.87965939999999</v>
+        <v>62.97895800000001</v>
       </c>
       <c r="N31">
-        <v>245.7203406</v>
+        <v>243.621042</v>
       </c>
       <c r="O31">
-        <v>61.43008515</v>
+        <v>60.90526049999999</v>
       </c>
       <c r="P31">
-        <v>184.29025545</v>
+        <v>182.7157815</v>
       </c>
       <c r="Q31">
-        <v>304.59025545</v>
+        <v>303.0157814999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09790016002412219</v>
+        <v>0.09850201015917173</v>
       </c>
       <c r="T31">
-        <v>0.8059729057367211</v>
+        <v>0.8152833359146578</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.036164837676473</v>
+        <v>4.86829267642059</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08139390711142021</v>
+        <v>0.08125095060571366</v>
       </c>
       <c r="C32">
-        <v>3024.995803287431</v>
+        <v>3003.537904259377</v>
       </c>
       <c r="D32">
-        <v>4092.75580328743</v>
+        <v>4109.259904259377</v>
       </c>
       <c r="E32">
-        <v>555.4600000000002</v>
+        <v>593.4220000000001</v>
       </c>
       <c r="F32">
-        <v>1138.86</v>
+        <v>1176.822</v>
       </c>
       <c r="G32">
         <v>71.09999999999999</v>
@@ -3911,28 +3911,28 @@
         <v>306.6</v>
       </c>
       <c r="M32">
-        <v>62.97895800000001</v>
+        <v>65.0782566</v>
       </c>
       <c r="N32">
-        <v>243.621042</v>
+        <v>241.5217434</v>
       </c>
       <c r="O32">
-        <v>60.90526049999999</v>
+        <v>60.38043584999999</v>
       </c>
       <c r="P32">
-        <v>182.7157815</v>
+        <v>181.14130755</v>
       </c>
       <c r="Q32">
-        <v>303.0157814999999</v>
+        <v>301.44130755</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09850201015917173</v>
+        <v>0.09912130522567197</v>
       </c>
       <c r="T32">
-        <v>0.8152833359146578</v>
+        <v>0.824863633633984</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.86829267642059</v>
+        <v>4.711250977181217</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08125095060571366</v>
+        <v>0.08110799410000713</v>
       </c>
       <c r="C33">
-        <v>3003.537904259377</v>
+        <v>2982.213650240895</v>
       </c>
       <c r="D33">
-        <v>4109.259904259377</v>
+        <v>4125.897650240895</v>
       </c>
       <c r="E33">
-        <v>593.4220000000001</v>
+        <v>631.3840000000001</v>
       </c>
       <c r="F33">
-        <v>1176.822</v>
+        <v>1214.784</v>
       </c>
       <c r="G33">
         <v>71.09999999999999</v>
@@ -3993,28 +3993,28 @@
         <v>306.6</v>
       </c>
       <c r="M33">
-        <v>65.0782566</v>
+        <v>67.17755520000001</v>
       </c>
       <c r="N33">
-        <v>241.5217434</v>
+        <v>239.4224447999999</v>
       </c>
       <c r="O33">
-        <v>60.38043584999999</v>
+        <v>59.85561119999998</v>
       </c>
       <c r="P33">
-        <v>181.14130755</v>
+        <v>179.5668335999999</v>
       </c>
       <c r="Q33">
-        <v>301.44130755</v>
+        <v>299.8668335999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09912130522567197</v>
+        <v>0.09975881485295165</v>
       </c>
       <c r="T33">
-        <v>0.824863633633984</v>
+        <v>0.8347257048156433</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.711250977181217</v>
+        <v>4.564024384144302</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08110799410000713</v>
+        <v>0.08158378759430059</v>
       </c>
       <c r="C34">
-        <v>2982.213650240895</v>
+        <v>2889.392302137176</v>
       </c>
       <c r="D34">
-        <v>4125.897650240895</v>
+        <v>4071.038302137176</v>
       </c>
       <c r="E34">
-        <v>631.3840000000001</v>
+        <v>669.3460000000001</v>
       </c>
       <c r="F34">
-        <v>1214.784</v>
+        <v>1252.746</v>
       </c>
       <c r="G34">
         <v>71.09999999999999</v>
@@ -4075,45 +4075,45 @@
         <v>306.6</v>
       </c>
       <c r="M34">
-        <v>67.17755520000001</v>
+        <v>72.40871880000002</v>
       </c>
       <c r="N34">
-        <v>239.4224447999999</v>
+        <v>234.1912811999999</v>
       </c>
       <c r="O34">
-        <v>59.85561119999998</v>
+        <v>58.54782029999998</v>
       </c>
       <c r="P34">
-        <v>179.5668335999999</v>
+        <v>175.6434609</v>
       </c>
       <c r="Q34">
-        <v>299.8668335999999</v>
+        <v>295.9434608999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09975881485295165</v>
+        <v>0.1004153546183591</v>
       </c>
       <c r="T34">
-        <v>0.8347257048156433</v>
+        <v>0.8448821661818299</v>
       </c>
       <c r="U34">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.564024384144302</v>
+        <v>4.234296712898059</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08158378759430059</v>
+        <v>0.08145958108859404</v>
       </c>
       <c r="C35">
-        <v>2889.392302137176</v>
+        <v>2865.610206293922</v>
       </c>
       <c r="D35">
-        <v>4071.038302137176</v>
+        <v>4085.218206293922</v>
       </c>
       <c r="E35">
-        <v>669.3460000000001</v>
+        <v>707.3080000000001</v>
       </c>
       <c r="F35">
-        <v>1252.746</v>
+        <v>1290.708</v>
       </c>
       <c r="G35">
         <v>71.09999999999999</v>
@@ -4157,28 +4157,28 @@
         <v>306.6</v>
       </c>
       <c r="M35">
-        <v>72.40871880000002</v>
+        <v>74.60292240000001</v>
       </c>
       <c r="N35">
-        <v>234.1912811999999</v>
+        <v>231.9970776</v>
       </c>
       <c r="O35">
-        <v>58.54782029999998</v>
+        <v>57.99926939999999</v>
       </c>
       <c r="P35">
-        <v>175.6434609</v>
+        <v>173.9978082</v>
       </c>
       <c r="Q35">
-        <v>295.9434608999999</v>
+        <v>294.2978082</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1004153546183591</v>
+        <v>0.1010917895281728</v>
       </c>
       <c r="T35">
-        <v>0.8448821661818299</v>
+        <v>0.8553463991045673</v>
       </c>
       <c r="U35">
         <v>0.0578</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.234296712898059</v>
+        <v>4.109758574283411</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08145958108859404</v>
+        <v>0.0822541245828875</v>
       </c>
       <c r="C36">
-        <v>2865.610206293922</v>
+        <v>2738.60797872791</v>
       </c>
       <c r="D36">
-        <v>4085.218206293922</v>
+        <v>3996.17797872791</v>
       </c>
       <c r="E36">
-        <v>707.3080000000001</v>
+        <v>745.2700000000003</v>
       </c>
       <c r="F36">
-        <v>1290.708</v>
+        <v>1328.67</v>
       </c>
       <c r="G36">
         <v>71.09999999999999</v>
@@ -4239,45 +4239,45 @@
         <v>306.6</v>
       </c>
       <c r="M36">
-        <v>74.60292240000001</v>
+        <v>81.44747100000002</v>
       </c>
       <c r="N36">
-        <v>231.9970776</v>
+        <v>225.152529</v>
       </c>
       <c r="O36">
-        <v>57.99926939999999</v>
+        <v>56.28813224999999</v>
       </c>
       <c r="P36">
-        <v>173.9978082</v>
+        <v>168.86439675</v>
       </c>
       <c r="Q36">
-        <v>294.2978082</v>
+        <v>289.16439675</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1010917895281728</v>
+        <v>0.1017890378198269</v>
       </c>
       <c r="T36">
-        <v>0.8553463991045673</v>
+        <v>0.8661326084249276</v>
       </c>
       <c r="U36">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>4.109758574283411</v>
+        <v>3.764389443104991</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0822541245828875</v>
+        <v>0.08215616807718096</v>
       </c>
       <c r="C37">
-        <v>2738.60797872791</v>
+        <v>2711.413109910344</v>
       </c>
       <c r="D37">
-        <v>3996.17797872791</v>
+        <v>4006.945109910344</v>
       </c>
       <c r="E37">
-        <v>745.2700000000003</v>
+        <v>783.2320000000003</v>
       </c>
       <c r="F37">
-        <v>1328.67</v>
+        <v>1366.632</v>
       </c>
       <c r="G37">
         <v>71.09999999999999</v>
@@ -4321,28 +4321,28 @@
         <v>306.6</v>
       </c>
       <c r="M37">
-        <v>81.44747100000002</v>
+        <v>83.77454160000002</v>
       </c>
       <c r="N37">
-        <v>225.152529</v>
+        <v>222.8254583999999</v>
       </c>
       <c r="O37">
-        <v>56.28813224999999</v>
+        <v>55.70636459999999</v>
       </c>
       <c r="P37">
-        <v>168.86439675</v>
+        <v>167.1190938</v>
       </c>
       <c r="Q37">
-        <v>289.16439675</v>
+        <v>287.4190938</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1017890378198269</v>
+        <v>0.1025080751205953</v>
       </c>
       <c r="T37">
-        <v>0.8661326084249276</v>
+        <v>0.8772558867865491</v>
       </c>
       <c r="U37">
         <v>0.0613</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.764389443104991</v>
+        <v>3.659823069685408</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08215616807718096</v>
+        <v>0.08205821157147443</v>
       </c>
       <c r="C38">
-        <v>2711.413109910344</v>
+        <v>2684.276418840735</v>
       </c>
       <c r="D38">
-        <v>4006.945109910344</v>
+        <v>4017.770418840735</v>
       </c>
       <c r="E38">
-        <v>783.2320000000001</v>
+        <v>821.1940000000001</v>
       </c>
       <c r="F38">
-        <v>1366.632</v>
+        <v>1404.594</v>
       </c>
       <c r="G38">
         <v>71.09999999999999</v>
@@ -4403,28 +4403,28 @@
         <v>306.6</v>
       </c>
       <c r="M38">
-        <v>83.77454160000001</v>
+        <v>86.10161220000001</v>
       </c>
       <c r="N38">
-        <v>222.8254583999999</v>
+        <v>220.4983878</v>
       </c>
       <c r="O38">
-        <v>55.70636459999999</v>
+        <v>55.12459694999999</v>
       </c>
       <c r="P38">
-        <v>167.1190938</v>
+        <v>165.37379085</v>
       </c>
       <c r="Q38">
-        <v>287.4190938</v>
+        <v>285.67379085</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1025080751205953</v>
+        <v>0.1032499390023403</v>
       </c>
       <c r="T38">
-        <v>0.8772558867865491</v>
+        <v>0.8887322850961585</v>
       </c>
       <c r="U38">
         <v>0.0613</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.659823069685408</v>
+        <v>3.560908932666884</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08205821157147443</v>
+        <v>0.08275825506576789</v>
       </c>
       <c r="C39">
-        <v>2684.276418840735</v>
+        <v>2570.211961128132</v>
       </c>
       <c r="D39">
-        <v>4017.770418840735</v>
+        <v>3941.667961128132</v>
       </c>
       <c r="E39">
-        <v>821.1940000000001</v>
+        <v>859.1560000000001</v>
       </c>
       <c r="F39">
-        <v>1404.594</v>
+        <v>1442.556</v>
       </c>
       <c r="G39">
         <v>71.09999999999999</v>
@@ -4485,45 +4485,45 @@
         <v>306.6</v>
       </c>
       <c r="M39">
-        <v>86.10161220000001</v>
+        <v>92.4678396</v>
       </c>
       <c r="N39">
-        <v>220.4983878</v>
+        <v>214.1321604</v>
       </c>
       <c r="O39">
-        <v>55.12459694999999</v>
+        <v>53.53304009999999</v>
       </c>
       <c r="P39">
-        <v>165.37379085</v>
+        <v>160.5991203</v>
       </c>
       <c r="Q39">
-        <v>285.67379085</v>
+        <v>280.8991203</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1032499390023403</v>
+        <v>0.104015733977045</v>
       </c>
       <c r="T39">
-        <v>0.8887322850961585</v>
+        <v>0.9005788898028522</v>
       </c>
       <c r="U39">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.560908932666884</v>
+        <v>3.315747413655374</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08275825506576789</v>
+        <v>0.08268129856006134</v>
       </c>
       <c r="C40">
-        <v>2570.211961128132</v>
+        <v>2540.474644227343</v>
       </c>
       <c r="D40">
-        <v>3941.667961128132</v>
+        <v>3949.892644227343</v>
       </c>
       <c r="E40">
-        <v>859.1560000000001</v>
+        <v>897.1180000000003</v>
       </c>
       <c r="F40">
-        <v>1442.556</v>
+        <v>1480.518</v>
       </c>
       <c r="G40">
         <v>71.09999999999999</v>
@@ -4567,28 +4567,28 @@
         <v>306.6</v>
       </c>
       <c r="M40">
-        <v>92.4678396</v>
+        <v>94.90120380000002</v>
       </c>
       <c r="N40">
-        <v>214.1321604</v>
+        <v>211.6987961999999</v>
       </c>
       <c r="O40">
-        <v>53.53304009999999</v>
+        <v>52.92469904999999</v>
       </c>
       <c r="P40">
-        <v>160.5991203</v>
+        <v>158.77409715</v>
       </c>
       <c r="Q40">
-        <v>280.8991203</v>
+        <v>279.0740971499999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.104015733977045</v>
+        <v>0.1048066369837071</v>
       </c>
       <c r="T40">
-        <v>0.9005788898028522</v>
+        <v>0.9128139077786178</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.315747413655374</v>
+        <v>3.230728249202671</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08268129856006134</v>
+        <v>0.0826043420543548</v>
       </c>
       <c r="C41">
-        <v>2540.474644227343</v>
+        <v>2510.771722337388</v>
       </c>
       <c r="D41">
-        <v>3949.892644227343</v>
+        <v>3958.151722337388</v>
       </c>
       <c r="E41">
-        <v>897.1180000000003</v>
+        <v>935.0800000000003</v>
       </c>
       <c r="F41">
-        <v>1480.518</v>
+        <v>1518.48</v>
       </c>
       <c r="G41">
         <v>71.09999999999999</v>
@@ -4649,28 +4649,28 @@
         <v>306.6</v>
       </c>
       <c r="M41">
-        <v>94.90120380000002</v>
+        <v>97.33456800000002</v>
       </c>
       <c r="N41">
-        <v>211.6987961999999</v>
+        <v>209.2654319999999</v>
       </c>
       <c r="O41">
-        <v>52.92469904999999</v>
+        <v>52.31635799999999</v>
       </c>
       <c r="P41">
-        <v>158.77409715</v>
+        <v>156.949074</v>
       </c>
       <c r="Q41">
-        <v>279.0740971499999</v>
+        <v>277.249074</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1048066369837071</v>
+        <v>0.1056239034239247</v>
       </c>
       <c r="T41">
-        <v>0.9128139077786178</v>
+        <v>0.9254567596869089</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.230728249202671</v>
+        <v>3.149960042972605</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0826043420543548</v>
+        <v>0.08252738554864826</v>
       </c>
       <c r="C42">
-        <v>2510.771722337388</v>
+        <v>2481.103411666401</v>
       </c>
       <c r="D42">
-        <v>3958.151722337388</v>
+        <v>3966.445411666402</v>
       </c>
       <c r="E42">
-        <v>935.0800000000003</v>
+        <v>973.0420000000003</v>
       </c>
       <c r="F42">
-        <v>1518.48</v>
+        <v>1556.442</v>
       </c>
       <c r="G42">
         <v>71.09999999999999</v>
@@ -4731,28 +4731,28 @@
         <v>306.6</v>
       </c>
       <c r="M42">
-        <v>97.33456800000002</v>
+        <v>99.76793220000002</v>
       </c>
       <c r="N42">
-        <v>209.2654319999999</v>
+        <v>206.8320677999999</v>
       </c>
       <c r="O42">
-        <v>52.31635799999999</v>
+        <v>51.70801694999999</v>
       </c>
       <c r="P42">
-        <v>156.949074</v>
+        <v>155.1240508499999</v>
       </c>
       <c r="Q42">
-        <v>277.249074</v>
+        <v>275.42405085</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1056239034239247</v>
+        <v>0.1064688738112682</v>
       </c>
       <c r="T42">
-        <v>0.9254567596869089</v>
+        <v>0.9385281828463286</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.149960042972605</v>
+        <v>3.073131749241565</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08252738554864826</v>
+        <v>0.08490742904294171</v>
       </c>
       <c r="C43">
-        <v>2481.103411666401</v>
+        <v>2201.747056973823</v>
       </c>
       <c r="D43">
-        <v>3966.445411666402</v>
+        <v>3725.051056973823</v>
       </c>
       <c r="E43">
-        <v>973.0420000000003</v>
+        <v>1011.004</v>
       </c>
       <c r="F43">
-        <v>1556.442</v>
+        <v>1594.404</v>
       </c>
       <c r="G43">
         <v>71.09999999999999</v>
@@ -4813,45 +4813,45 @@
         <v>306.6</v>
       </c>
       <c r="M43">
-        <v>99.76793220000002</v>
+        <v>114.6376476</v>
       </c>
       <c r="N43">
-        <v>206.8320677999999</v>
+        <v>191.9623523999999</v>
       </c>
       <c r="O43">
-        <v>51.70801694999999</v>
+        <v>47.99058809999998</v>
       </c>
       <c r="P43">
-        <v>155.1240508499999</v>
+        <v>143.9717643</v>
       </c>
       <c r="Q43">
-        <v>275.42405085</v>
+        <v>264.2717643</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1064688738112682</v>
+        <v>0.1073429811085202</v>
       </c>
       <c r="T43">
-        <v>0.9385281828463286</v>
+        <v>0.9520503447353833</v>
       </c>
       <c r="U43">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>3.073131749241565</v>
+        <v>2.674514057282521</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08490742904294173</v>
+        <v>0.08488897253723518</v>
       </c>
       <c r="C44">
-        <v>2201.747056973822</v>
+        <v>2165.543901518142</v>
       </c>
       <c r="D44">
-        <v>3725.051056973822</v>
+        <v>3726.809901518142</v>
       </c>
       <c r="E44">
-        <v>1011.004</v>
+        <v>1048.966</v>
       </c>
       <c r="F44">
-        <v>1594.404</v>
+        <v>1632.366</v>
       </c>
       <c r="G44">
         <v>71.09999999999999</v>
@@ -4895,28 +4895,28 @@
         <v>306.6</v>
       </c>
       <c r="M44">
-        <v>114.6376476</v>
+        <v>117.3671154</v>
       </c>
       <c r="N44">
-        <v>191.9623524</v>
+        <v>189.2328846</v>
       </c>
       <c r="O44">
-        <v>47.99058809999999</v>
+        <v>47.30822114999999</v>
       </c>
       <c r="P44">
-        <v>143.9717643</v>
+        <v>141.92466345</v>
       </c>
       <c r="Q44">
-        <v>264.2717643</v>
+        <v>262.22466345</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1073429811085202</v>
+        <v>0.1082477588372547</v>
       </c>
       <c r="T44">
-        <v>0.9520503447353833</v>
+        <v>0.9660469684451065</v>
       </c>
       <c r="U44">
         <v>0.07190000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.674514057282522</v>
+        <v>2.61231605595037</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08488897253723518</v>
+        <v>0.08487051603152863</v>
       </c>
       <c r="C45">
-        <v>2165.543901518142</v>
+        <v>2129.342407782227</v>
       </c>
       <c r="D45">
-        <v>3726.809901518142</v>
+        <v>3728.570407782228</v>
       </c>
       <c r="E45">
-        <v>1048.966</v>
+        <v>1086.928</v>
       </c>
       <c r="F45">
-        <v>1632.366</v>
+        <v>1670.328</v>
       </c>
       <c r="G45">
         <v>71.09999999999999</v>
@@ -4977,28 +4977,28 @@
         <v>306.6</v>
       </c>
       <c r="M45">
-        <v>117.3671154</v>
+        <v>120.0965832</v>
       </c>
       <c r="N45">
-        <v>189.2328846</v>
+        <v>186.5034167999999</v>
       </c>
       <c r="O45">
-        <v>47.30822114999999</v>
+        <v>46.62585419999998</v>
       </c>
       <c r="P45">
-        <v>141.92466345</v>
+        <v>139.8775625999999</v>
       </c>
       <c r="Q45">
-        <v>262.22466345</v>
+        <v>260.1775625999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1082477588372547</v>
+        <v>0.1091848500563011</v>
       </c>
       <c r="T45">
-        <v>0.9660469684451065</v>
+        <v>0.9805434715730345</v>
       </c>
       <c r="U45">
         <v>0.07190000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.61231605595037</v>
+        <v>2.552945236496952</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08487051603152863</v>
+        <v>0.08616830952582211</v>
       </c>
       <c r="C46">
-        <v>2129.342407782227</v>
+        <v>1971.511270950039</v>
       </c>
       <c r="D46">
-        <v>3728.570407782228</v>
+        <v>3608.701270950039</v>
       </c>
       <c r="E46">
-        <v>1086.928</v>
+        <v>1124.89</v>
       </c>
       <c r="F46">
-        <v>1670.328</v>
+        <v>1708.29</v>
       </c>
       <c r="G46">
         <v>71.09999999999999</v>
@@ -5059,45 +5059,45 @@
         <v>306.6</v>
       </c>
       <c r="M46">
-        <v>120.0965832</v>
+        <v>129.488382</v>
       </c>
       <c r="N46">
-        <v>186.5034167999999</v>
+        <v>177.1116179999999</v>
       </c>
       <c r="O46">
-        <v>46.62585419999998</v>
+        <v>44.27790449999998</v>
       </c>
       <c r="P46">
-        <v>139.8775625999999</v>
+        <v>132.8337135</v>
       </c>
       <c r="Q46">
-        <v>260.1775625999999</v>
+        <v>253.1337134999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1091848500563011</v>
+        <v>0.1101560173196765</v>
       </c>
       <c r="T46">
-        <v>0.9805434715730345</v>
+        <v>0.9955671202692504</v>
       </c>
       <c r="U46">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.552945236496952</v>
+        <v>2.367779991258211</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08616830952582211</v>
+        <v>0.08617910302011556</v>
       </c>
       <c r="C47">
-        <v>1971.511270950039</v>
+        <v>1932.584650796011</v>
       </c>
       <c r="D47">
-        <v>3608.701270950039</v>
+        <v>3607.736650796011</v>
       </c>
       <c r="E47">
-        <v>1124.89</v>
+        <v>1162.852</v>
       </c>
       <c r="F47">
-        <v>1708.29</v>
+        <v>1746.252</v>
       </c>
       <c r="G47">
         <v>71.09999999999999</v>
@@ -5141,28 +5141,28 @@
         <v>306.6</v>
       </c>
       <c r="M47">
-        <v>129.488382</v>
+        <v>132.3659016</v>
       </c>
       <c r="N47">
-        <v>177.1116179999999</v>
+        <v>174.2340983999999</v>
       </c>
       <c r="O47">
-        <v>44.27790449999998</v>
+        <v>43.55852459999998</v>
       </c>
       <c r="P47">
-        <v>132.8337135</v>
+        <v>130.6755737999999</v>
       </c>
       <c r="Q47">
-        <v>253.1337134999999</v>
+        <v>250.9755737999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1101560173196765</v>
+        <v>0.1111631537409547</v>
       </c>
       <c r="T47">
-        <v>0.9955671202692504</v>
+        <v>1.01114720039866</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.367779991258211</v>
+        <v>2.316306513187381</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08617910302011556</v>
+        <v>0.08618989651440902</v>
       </c>
       <c r="C48">
-        <v>1932.584650796011</v>
+        <v>1893.658546197754</v>
       </c>
       <c r="D48">
-        <v>3607.736650796011</v>
+        <v>3606.772546197754</v>
       </c>
       <c r="E48">
-        <v>1162.852</v>
+        <v>1200.814</v>
       </c>
       <c r="F48">
-        <v>1746.252</v>
+        <v>1784.214</v>
       </c>
       <c r="G48">
         <v>71.09999999999999</v>
@@ -5223,28 +5223,28 @@
         <v>306.6</v>
       </c>
       <c r="M48">
-        <v>132.3659016</v>
+        <v>135.2434212</v>
       </c>
       <c r="N48">
-        <v>174.2340983999999</v>
+        <v>171.3565787999999</v>
       </c>
       <c r="O48">
-        <v>43.55852459999998</v>
+        <v>42.83914469999998</v>
       </c>
       <c r="P48">
-        <v>130.6755737999999</v>
+        <v>128.5174340999999</v>
       </c>
       <c r="Q48">
-        <v>250.9755737999999</v>
+        <v>248.8174341</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1111631537409547</v>
+        <v>0.1122082953102057</v>
       </c>
       <c r="T48">
-        <v>1.01114720039866</v>
+        <v>1.027315208080122</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.316306513187381</v>
+        <v>2.267023395885521</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08618989651440902</v>
+        <v>0.08620069000870248</v>
       </c>
       <c r="C49">
-        <v>1893.658546197754</v>
+        <v>1854.732956742058</v>
       </c>
       <c r="D49">
-        <v>3606.772546197754</v>
+        <v>3605.808956742059</v>
       </c>
       <c r="E49">
-        <v>1200.814</v>
+        <v>1238.776</v>
       </c>
       <c r="F49">
-        <v>1784.214</v>
+        <v>1822.176</v>
       </c>
       <c r="G49">
         <v>71.09999999999999</v>
@@ -5305,28 +5305,28 @@
         <v>306.6</v>
       </c>
       <c r="M49">
-        <v>135.2434212</v>
+        <v>138.1209408</v>
       </c>
       <c r="N49">
-        <v>171.3565787999999</v>
+        <v>168.4790591999999</v>
       </c>
       <c r="O49">
-        <v>42.83914469999998</v>
+        <v>42.11976479999998</v>
       </c>
       <c r="P49">
-        <v>128.5174340999999</v>
+        <v>126.3592944</v>
       </c>
       <c r="Q49">
-        <v>248.8174341</v>
+        <v>246.6592944</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1122082953102057</v>
+        <v>0.1132936346321201</v>
       </c>
       <c r="T49">
-        <v>1.027315208080122</v>
+        <v>1.044105062210872</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.267023395885521</v>
+        <v>2.219793741804573</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08620069000870248</v>
+        <v>0.08621148350299593</v>
       </c>
       <c r="C50">
-        <v>1854.732956742059</v>
+        <v>1815.807882016158</v>
       </c>
       <c r="D50">
-        <v>3605.808956742059</v>
+        <v>3604.845882016159</v>
       </c>
       <c r="E50">
-        <v>1238.776</v>
+        <v>1276.738</v>
       </c>
       <c r="F50">
-        <v>1822.176</v>
+        <v>1860.138</v>
       </c>
       <c r="G50">
         <v>71.09999999999999</v>
@@ -5387,28 +5387,28 @@
         <v>306.6</v>
       </c>
       <c r="M50">
-        <v>138.1209408</v>
+        <v>140.9984604</v>
       </c>
       <c r="N50">
-        <v>168.4790591999999</v>
+        <v>165.6015395999999</v>
       </c>
       <c r="O50">
-        <v>42.11976479999998</v>
+        <v>41.40038489999998</v>
       </c>
       <c r="P50">
-        <v>126.3592944</v>
+        <v>124.2011547</v>
       </c>
       <c r="Q50">
-        <v>246.6592944</v>
+        <v>244.5011547</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1132936346321201</v>
+        <v>0.1144215362803842</v>
       </c>
       <c r="T50">
-        <v>1.044105062210872</v>
+        <v>1.061553341993807</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.219793741804573</v>
+        <v>2.17449182870652</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08621148350299593</v>
+        <v>0.08622227699728939</v>
       </c>
       <c r="C51">
-        <v>1815.807882016158</v>
+        <v>1776.883321607724</v>
       </c>
       <c r="D51">
-        <v>3604.845882016159</v>
+        <v>3603.883321607725</v>
       </c>
       <c r="E51">
-        <v>1276.738</v>
+        <v>1314.7</v>
       </c>
       <c r="F51">
-        <v>1860.138</v>
+        <v>1898.1</v>
       </c>
       <c r="G51">
         <v>71.09999999999999</v>
@@ -5469,28 +5469,28 @@
         <v>306.6</v>
       </c>
       <c r="M51">
-        <v>140.9984604</v>
+        <v>143.87598</v>
       </c>
       <c r="N51">
-        <v>165.6015395999999</v>
+        <v>162.7240199999999</v>
       </c>
       <c r="O51">
-        <v>41.40038489999998</v>
+        <v>40.68100499999998</v>
       </c>
       <c r="P51">
-        <v>124.2011547</v>
+        <v>122.043015</v>
       </c>
       <c r="Q51">
-        <v>244.5011547</v>
+        <v>242.343015</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1144215362803842</v>
+        <v>0.1155945539945788</v>
       </c>
       <c r="T51">
-        <v>1.061553341993807</v>
+        <v>1.07969955296806</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.17449182870652</v>
+        <v>2.13100199213239</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08622227699728939</v>
+        <v>0.08623307049158285</v>
       </c>
       <c r="C52">
-        <v>1776.883321607724</v>
+        <v>1737.95927510487</v>
       </c>
       <c r="D52">
-        <v>3603.883321607725</v>
+        <v>3602.92127510487</v>
       </c>
       <c r="E52">
-        <v>1314.7</v>
+        <v>1352.662</v>
       </c>
       <c r="F52">
-        <v>1898.1</v>
+        <v>1936.062</v>
       </c>
       <c r="G52">
         <v>71.09999999999999</v>
@@ -5551,28 +5551,28 @@
         <v>306.6</v>
       </c>
       <c r="M52">
-        <v>143.87598</v>
+        <v>146.7534996</v>
       </c>
       <c r="N52">
-        <v>162.7240199999999</v>
+        <v>159.8465003999999</v>
       </c>
       <c r="O52">
-        <v>40.68100499999998</v>
+        <v>39.96162509999998</v>
       </c>
       <c r="P52">
-        <v>122.043015</v>
+        <v>119.8848752999999</v>
       </c>
       <c r="Q52">
-        <v>242.343015</v>
+        <v>240.1848752999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1155945539945788</v>
+        <v>0.1168154499828221</v>
       </c>
       <c r="T52">
-        <v>1.07969955296806</v>
+        <v>1.098586425614732</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.13100199213239</v>
+        <v>2.08921763934548</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08623307049158285</v>
+        <v>0.0862438639858763</v>
       </c>
       <c r="C53">
-        <v>1737.95927510487</v>
+        <v>1699.035742096151</v>
       </c>
       <c r="D53">
-        <v>3602.92127510487</v>
+        <v>3601.959742096151</v>
       </c>
       <c r="E53">
-        <v>1352.662</v>
+        <v>1390.624</v>
       </c>
       <c r="F53">
-        <v>1936.062</v>
+        <v>1974.024</v>
       </c>
       <c r="G53">
         <v>71.09999999999999</v>
@@ -5633,28 +5633,28 @@
         <v>306.6</v>
       </c>
       <c r="M53">
-        <v>146.7534996</v>
+        <v>149.6310192</v>
       </c>
       <c r="N53">
-        <v>159.8465003999999</v>
+        <v>156.9689807999999</v>
       </c>
       <c r="O53">
-        <v>39.96162509999998</v>
+        <v>39.24224519999999</v>
       </c>
       <c r="P53">
-        <v>119.8848752999999</v>
+        <v>117.7267356</v>
       </c>
       <c r="Q53">
-        <v>240.1848752999999</v>
+        <v>238.0267355999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1168154499828221</v>
+        <v>0.1180872166372423</v>
       </c>
       <c r="T53">
-        <v>1.098586425614732</v>
+        <v>1.118260251288348</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.08921763934548</v>
+        <v>2.049040377050375</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0862438639858763</v>
+        <v>0.08625465748016976</v>
       </c>
       <c r="C54">
-        <v>1699.035742096151</v>
+        <v>1660.112722170555</v>
       </c>
       <c r="D54">
-        <v>3601.959742096151</v>
+        <v>3600.998722170556</v>
       </c>
       <c r="E54">
-        <v>1390.624</v>
+        <v>1428.586</v>
       </c>
       <c r="F54">
-        <v>1974.024</v>
+        <v>2011.986</v>
       </c>
       <c r="G54">
         <v>71.09999999999999</v>
@@ -5715,28 +5715,28 @@
         <v>306.6</v>
       </c>
       <c r="M54">
-        <v>149.6310192</v>
+        <v>152.5085388</v>
       </c>
       <c r="N54">
-        <v>156.9689807999999</v>
+        <v>154.0914611999999</v>
       </c>
       <c r="O54">
-        <v>39.24224519999999</v>
+        <v>38.52286529999999</v>
       </c>
       <c r="P54">
-        <v>117.7267356</v>
+        <v>115.5685959</v>
       </c>
       <c r="Q54">
-        <v>238.0267355999999</v>
+        <v>235.8685958999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1180872166372423</v>
+        <v>0.1194131010216378</v>
       </c>
       <c r="T54">
-        <v>1.118260251288348</v>
+        <v>1.138771261033182</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.049040377050375</v>
+        <v>2.010379237860746</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08625465748016976</v>
+        <v>0.09201645097446323</v>
       </c>
       <c r="C55">
-        <v>1660.112722170555</v>
+        <v>1173.215103513342</v>
       </c>
       <c r="D55">
-        <v>3600.998722170556</v>
+        <v>3152.063103513342</v>
       </c>
       <c r="E55">
-        <v>1428.586</v>
+        <v>1466.548</v>
       </c>
       <c r="F55">
-        <v>2011.986</v>
+        <v>2049.948</v>
       </c>
       <c r="G55">
         <v>71.09999999999999</v>
@@ -5797,45 +5797,45 @@
         <v>306.6</v>
       </c>
       <c r="M55">
-        <v>152.5085388</v>
+        <v>184.49532</v>
       </c>
       <c r="N55">
-        <v>154.0914611999999</v>
+        <v>122.1046799999999</v>
       </c>
       <c r="O55">
-        <v>38.52286529999999</v>
+        <v>30.52616999999999</v>
       </c>
       <c r="P55">
-        <v>115.5685959</v>
+        <v>91.57850999999997</v>
       </c>
       <c r="Q55">
-        <v>235.8685958999999</v>
+        <v>211.8785099999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1194131010216378</v>
+        <v>0.1207966325531809</v>
       </c>
       <c r="T55">
-        <v>1.138771261033182</v>
+        <v>1.1601740538104</v>
       </c>
       <c r="U55">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.010379237860746</v>
+        <v>1.661830771642337</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09201645097446323</v>
+        <v>0.09213374446875669</v>
       </c>
       <c r="C56">
-        <v>1173.215103513342</v>
+        <v>1127.273681606402</v>
       </c>
       <c r="D56">
-        <v>3152.063103513342</v>
+        <v>3144.083681606402</v>
       </c>
       <c r="E56">
-        <v>1466.548</v>
+        <v>1504.51</v>
       </c>
       <c r="F56">
-        <v>2049.948</v>
+        <v>2087.91</v>
       </c>
       <c r="G56">
         <v>71.09999999999999</v>
@@ -5879,28 +5879,28 @@
         <v>306.6</v>
       </c>
       <c r="M56">
-        <v>184.49532</v>
+        <v>187.9119</v>
       </c>
       <c r="N56">
-        <v>122.1046799999999</v>
+        <v>118.6880999999999</v>
       </c>
       <c r="O56">
-        <v>30.52616999999999</v>
+        <v>29.67202499999998</v>
       </c>
       <c r="P56">
-        <v>91.57850999999997</v>
+        <v>89.01607499999994</v>
       </c>
       <c r="Q56">
-        <v>211.8785099999999</v>
+        <v>209.316075</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1207966325531809</v>
+        <v>0.1222416543750149</v>
       </c>
       <c r="T56">
-        <v>1.1601740538104</v>
+        <v>1.182528081822162</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.661830771642337</v>
+        <v>1.631615666703385</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09213374446875669</v>
+        <v>0.09225103796305013</v>
       </c>
       <c r="C57">
-        <v>1127.273681606402</v>
+        <v>1081.372557368533</v>
       </c>
       <c r="D57">
-        <v>3144.083681606402</v>
+        <v>3136.144557368533</v>
       </c>
       <c r="E57">
-        <v>1504.51</v>
+        <v>1542.472</v>
       </c>
       <c r="F57">
-        <v>2087.91</v>
+        <v>2125.872</v>
       </c>
       <c r="G57">
         <v>71.09999999999999</v>
@@ -5961,28 +5961,28 @@
         <v>306.6</v>
       </c>
       <c r="M57">
-        <v>187.9119</v>
+        <v>191.32848</v>
       </c>
       <c r="N57">
-        <v>118.6880999999999</v>
+        <v>115.27152</v>
       </c>
       <c r="O57">
-        <v>29.67202499999998</v>
+        <v>28.81787999999999</v>
       </c>
       <c r="P57">
-        <v>89.01607499999994</v>
+        <v>86.45363999999996</v>
       </c>
       <c r="Q57">
-        <v>209.316075</v>
+        <v>206.75364</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1222416543750149</v>
+        <v>0.1237523590069321</v>
       </c>
       <c r="T57">
-        <v>1.182528081822162</v>
+        <v>1.205898202016275</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.631615666703385</v>
+        <v>1.602479672655111</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09225103796305013</v>
+        <v>0.09236833145734361</v>
       </c>
       <c r="C58">
-        <v>1081.372557368533</v>
+        <v>1035.511426301745</v>
       </c>
       <c r="D58">
-        <v>3136.144557368533</v>
+        <v>3128.245426301745</v>
       </c>
       <c r="E58">
-        <v>1542.472</v>
+        <v>1580.434</v>
       </c>
       <c r="F58">
-        <v>2125.872</v>
+        <v>2163.834</v>
       </c>
       <c r="G58">
         <v>71.09999999999999</v>
@@ -6043,28 +6043,28 @@
         <v>306.6</v>
       </c>
       <c r="M58">
-        <v>191.32848</v>
+        <v>194.74506</v>
       </c>
       <c r="N58">
-        <v>115.27152</v>
+        <v>111.8549399999999</v>
       </c>
       <c r="O58">
-        <v>28.81787999999999</v>
+        <v>27.96373499999999</v>
       </c>
       <c r="P58">
-        <v>86.45363999999996</v>
+        <v>83.89120499999996</v>
       </c>
       <c r="Q58">
-        <v>206.75364</v>
+        <v>204.191205</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1237523590069321</v>
+        <v>0.1253333289705665</v>
       </c>
       <c r="T58">
-        <v>1.205898202016275</v>
+        <v>1.230355304544999</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.602479672655111</v>
+        <v>1.574365994187477</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09236833145734361</v>
+        <v>0.09248562495163706</v>
       </c>
       <c r="C59">
-        <v>1035.511426301745</v>
+        <v>989.6899869681474</v>
       </c>
       <c r="D59">
-        <v>3128.245426301745</v>
+        <v>3120.385986968148</v>
       </c>
       <c r="E59">
-        <v>1580.434</v>
+        <v>1618.396</v>
       </c>
       <c r="F59">
-        <v>2163.834</v>
+        <v>2201.796</v>
       </c>
       <c r="G59">
         <v>71.09999999999999</v>
@@ -6125,28 +6125,28 @@
         <v>306.6</v>
       </c>
       <c r="M59">
-        <v>194.74506</v>
+        <v>198.16164</v>
       </c>
       <c r="N59">
-        <v>111.8549399999999</v>
+        <v>108.43836</v>
       </c>
       <c r="O59">
-        <v>27.96373499999999</v>
+        <v>27.10958999999999</v>
       </c>
       <c r="P59">
-        <v>83.89120499999996</v>
+        <v>81.32876999999996</v>
       </c>
       <c r="Q59">
-        <v>204.191205</v>
+        <v>201.62877</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1253333289705665</v>
+        <v>0.1269895832181835</v>
       </c>
       <c r="T59">
-        <v>1.230355304544999</v>
+        <v>1.255977031003662</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.574365994187477</v>
+        <v>1.547221752908383</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09248562495163706</v>
+        <v>0.09260291844593052</v>
       </c>
       <c r="C60">
-        <v>989.6899869681479</v>
+        <v>943.9079409516012</v>
       </c>
       <c r="D60">
-        <v>3120.385986968148</v>
+        <v>3112.565940951602</v>
       </c>
       <c r="E60">
-        <v>1618.396</v>
+        <v>1656.358</v>
       </c>
       <c r="F60">
-        <v>2201.796</v>
+        <v>2239.758</v>
       </c>
       <c r="G60">
         <v>71.09999999999999</v>
@@ -6207,28 +6207,28 @@
         <v>306.6</v>
       </c>
       <c r="M60">
-        <v>198.16164</v>
+        <v>201.57822</v>
       </c>
       <c r="N60">
-        <v>108.43836</v>
+        <v>105.0217799999999</v>
       </c>
       <c r="O60">
-        <v>27.10959</v>
+        <v>26.25544499999999</v>
       </c>
       <c r="P60">
-        <v>81.32876999999999</v>
+        <v>78.76633499999997</v>
       </c>
       <c r="Q60">
-        <v>201.62877</v>
+        <v>199.066335</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1269895832181835</v>
+        <v>0.1287266303559281</v>
       </c>
       <c r="T60">
-        <v>1.255977031003662</v>
+        <v>1.282848597777382</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.547221752908383</v>
+        <v>1.520997655401461</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09260291844593052</v>
+        <v>0.1206058042581425</v>
       </c>
       <c r="C61">
-        <v>943.9079409516012</v>
+        <v>-259.2153656051773</v>
       </c>
       <c r="D61">
-        <v>3112.565940951602</v>
+        <v>1947.404634394823</v>
       </c>
       <c r="E61">
-        <v>1656.358</v>
+        <v>1694.32</v>
       </c>
       <c r="F61">
-        <v>2239.758</v>
+        <v>2277.72</v>
       </c>
       <c r="G61">
         <v>71.09999999999999</v>
@@ -6289,45 +6289,45 @@
         <v>306.6</v>
       </c>
       <c r="M61">
-        <v>201.57822</v>
+        <v>334.3692960000001</v>
       </c>
       <c r="N61">
-        <v>105.0217799999999</v>
+        <v>-27.76929600000011</v>
       </c>
       <c r="O61">
-        <v>26.25544499999999</v>
+        <v>-6.942324000000028</v>
       </c>
       <c r="P61">
-        <v>78.76633499999997</v>
+        <v>-20.82697200000008</v>
       </c>
       <c r="Q61">
-        <v>199.066335</v>
+        <v>99.47302799999991</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1287266303559281</v>
+        <v>0.1317926203339923</v>
       </c>
       <c r="T61">
-        <v>1.282848597777382</v>
+        <v>1.330278487636376</v>
       </c>
       <c r="U61">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.25</v>
+        <v>0.2292375553525703</v>
       </c>
       <c r="W61">
-        <v>0.0675</v>
+        <v>0.1131479268742427</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y61">
-        <v>1.520997655401461</v>
+        <v>0.9169502214102814</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1206058042581425</v>
+        <v>0.1216158042581426</v>
       </c>
       <c r="C62">
-        <v>-259.2153656051773</v>
+        <v>-323.1202240894299</v>
       </c>
       <c r="D62">
-        <v>1947.404634394823</v>
+        <v>1921.46177591057</v>
       </c>
       <c r="E62">
-        <v>1694.32</v>
+        <v>1732.282</v>
       </c>
       <c r="F62">
-        <v>2277.72</v>
+        <v>2315.682</v>
       </c>
       <c r="G62">
         <v>71.09999999999999</v>
@@ -6371,37 +6371,37 @@
         <v>306.6</v>
       </c>
       <c r="M62">
-        <v>334.3692960000001</v>
+        <v>339.9421176000001</v>
       </c>
       <c r="N62">
-        <v>-27.76929600000011</v>
+        <v>-33.34211760000011</v>
       </c>
       <c r="O62">
-        <v>-6.942324000000028</v>
+        <v>-8.335529400000027</v>
       </c>
       <c r="P62">
-        <v>-20.82697200000008</v>
+        <v>-25.00658820000008</v>
       </c>
       <c r="Q62">
-        <v>99.47302799999991</v>
+        <v>95.29341179999992</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1317926203339923</v>
+        <v>0.1339975593169153</v>
       </c>
       <c r="T62">
-        <v>1.330278487636376</v>
+        <v>1.364388192447566</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2292375553525703</v>
+        <v>0.2254795626418725</v>
       </c>
       <c r="W62">
-        <v>0.1131479268742427</v>
+        <v>0.1136996002041731</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.9169502214102814</v>
+        <v>0.9019182505674899</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1216158042581426</v>
+        <v>0.1226258042581425</v>
       </c>
       <c r="C63">
-        <v>-323.1202240894299</v>
+        <v>-386.3429605361159</v>
       </c>
       <c r="D63">
-        <v>1921.46177591057</v>
+        <v>1896.201039463884</v>
       </c>
       <c r="E63">
-        <v>1732.282</v>
+        <v>1770.244</v>
       </c>
       <c r="F63">
-        <v>2315.682</v>
+        <v>2353.644</v>
       </c>
       <c r="G63">
         <v>71.09999999999999</v>
@@ -6453,37 +6453,37 @@
         <v>306.6</v>
       </c>
       <c r="M63">
-        <v>339.9421176000001</v>
+        <v>345.5149392000001</v>
       </c>
       <c r="N63">
-        <v>-33.34211760000011</v>
+        <v>-38.91493920000011</v>
       </c>
       <c r="O63">
-        <v>-8.335529400000027</v>
+        <v>-9.728734800000026</v>
       </c>
       <c r="P63">
-        <v>-25.00658820000008</v>
+        <v>-29.18620440000008</v>
       </c>
       <c r="Q63">
-        <v>95.29341179999992</v>
+        <v>91.11379559999992</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1339975593169153</v>
+        <v>0.1363185477199919</v>
       </c>
       <c r="T63">
-        <v>1.364388192447566</v>
+        <v>1.400293144880396</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.2254795626418725</v>
+        <v>0.2218427955024874</v>
       </c>
       <c r="W63">
-        <v>0.1136996002041731</v>
+        <v>0.1142334776202349</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.9019182505674899</v>
+        <v>0.8873711820099497</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1226258042581425</v>
+        <v>0.1236358042581426</v>
       </c>
       <c r="C64">
-        <v>-386.3429605361159</v>
+        <v>-448.9101286603754</v>
       </c>
       <c r="D64">
-        <v>1896.201039463884</v>
+        <v>1871.595871339625</v>
       </c>
       <c r="E64">
-        <v>1770.244</v>
+        <v>1808.206</v>
       </c>
       <c r="F64">
-        <v>2353.644</v>
+        <v>2391.606</v>
       </c>
       <c r="G64">
         <v>71.09999999999999</v>
@@ -6535,37 +6535,37 @@
         <v>306.6</v>
       </c>
       <c r="M64">
-        <v>345.5149392000001</v>
+        <v>351.0877608000001</v>
       </c>
       <c r="N64">
-        <v>-38.91493920000011</v>
+        <v>-44.4877608000001</v>
       </c>
       <c r="O64">
-        <v>-9.728734800000026</v>
+        <v>-11.12194020000003</v>
       </c>
       <c r="P64">
-        <v>-29.18620440000008</v>
+        <v>-33.36582060000008</v>
       </c>
       <c r="Q64">
-        <v>91.11379559999992</v>
+        <v>86.93417939999992</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1363185477199919</v>
+        <v>0.1387649949556674</v>
       </c>
       <c r="T64">
-        <v>1.400293144880396</v>
+        <v>1.43813890555284</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2218427955024874</v>
+        <v>0.2183214812881622</v>
       </c>
       <c r="W64">
-        <v>0.1142334776202349</v>
+        <v>0.1147504065468978</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8873711820099497</v>
+        <v>0.8732859251526489</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1236358042581426</v>
+        <v>0.1246458042581425</v>
       </c>
       <c r="C65">
-        <v>-448.9101286603754</v>
+        <v>-510.8469215848547</v>
       </c>
       <c r="D65">
-        <v>1871.595871339625</v>
+        <v>1847.621078415146</v>
       </c>
       <c r="E65">
-        <v>1808.206</v>
+        <v>1846.168</v>
       </c>
       <c r="F65">
-        <v>2391.606</v>
+        <v>2429.568</v>
       </c>
       <c r="G65">
         <v>71.09999999999999</v>
@@ -6617,37 +6617,37 @@
         <v>306.6</v>
       </c>
       <c r="M65">
-        <v>351.0877608000001</v>
+        <v>356.6605824000001</v>
       </c>
       <c r="N65">
-        <v>-44.4877608000001</v>
+        <v>-50.0605824000001</v>
       </c>
       <c r="O65">
-        <v>-11.12194020000003</v>
+        <v>-12.51514560000003</v>
       </c>
       <c r="P65">
-        <v>-33.36582060000008</v>
+        <v>-37.54543680000008</v>
       </c>
       <c r="Q65">
-        <v>86.93417939999992</v>
+        <v>82.75456319999992</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1387649949556674</v>
+        <v>0.1413473559266582</v>
       </c>
       <c r="T65">
-        <v>1.43813890555284</v>
+        <v>1.478087208484863</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2183214812881622</v>
+        <v>0.2149102081430347</v>
       </c>
       <c r="W65">
-        <v>0.1147504065468978</v>
+        <v>0.1152511814446025</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8732859251526489</v>
+        <v>0.8596408325721387</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1246458042581425</v>
+        <v>0.1256558042581425</v>
       </c>
       <c r="C66">
-        <v>-510.8469215848547</v>
+        <v>-572.1772578822006</v>
       </c>
       <c r="D66">
-        <v>1847.621078415146</v>
+        <v>1824.2527421178</v>
       </c>
       <c r="E66">
-        <v>1846.168</v>
+        <v>1884.13</v>
       </c>
       <c r="F66">
-        <v>2429.568</v>
+        <v>2467.53</v>
       </c>
       <c r="G66">
         <v>71.09999999999999</v>
@@ -6699,37 +6699,37 @@
         <v>306.6</v>
       </c>
       <c r="M66">
-        <v>356.6605824000001</v>
+        <v>362.2334040000001</v>
       </c>
       <c r="N66">
-        <v>-50.0605824000001</v>
+        <v>-55.6334040000001</v>
       </c>
       <c r="O66">
-        <v>-12.51514560000003</v>
+        <v>-13.90835100000002</v>
       </c>
       <c r="P66">
-        <v>-37.54543680000008</v>
+        <v>-41.72505300000007</v>
       </c>
       <c r="Q66">
-        <v>82.75456319999992</v>
+        <v>78.57494699999992</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1413473559266582</v>
+        <v>0.1440772803817056</v>
       </c>
       <c r="T66">
-        <v>1.478087208484863</v>
+        <v>1.520318271584431</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2149102081430347</v>
+        <v>0.2116038972485265</v>
       </c>
       <c r="W66">
-        <v>0.1152511814446025</v>
+        <v>0.1157365478839163</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8596408325721387</v>
+        <v>0.8464155889941058</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1256558042581425</v>
+        <v>0.1266658042581426</v>
       </c>
       <c r="C67">
-        <v>-572.1772578822006</v>
+        <v>-632.9238611696092</v>
       </c>
       <c r="D67">
-        <v>1824.2527421178</v>
+        <v>1801.468138830391</v>
       </c>
       <c r="E67">
-        <v>1884.13</v>
+        <v>1922.092</v>
       </c>
       <c r="F67">
-        <v>2467.53</v>
+        <v>2505.492</v>
       </c>
       <c r="G67">
         <v>71.09999999999999</v>
@@ -6781,37 +6781,37 @@
         <v>306.6</v>
       </c>
       <c r="M67">
-        <v>362.2334040000001</v>
+        <v>367.8062256000001</v>
       </c>
       <c r="N67">
-        <v>-55.6334040000001</v>
+        <v>-61.2062256000001</v>
       </c>
       <c r="O67">
-        <v>-13.90835100000002</v>
+        <v>-15.30155640000002</v>
       </c>
       <c r="P67">
-        <v>-41.72505300000007</v>
+        <v>-45.90466920000007</v>
       </c>
       <c r="Q67">
-        <v>78.57494699999992</v>
+        <v>74.39533079999993</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1440772803817056</v>
+        <v>0.1469677886282263</v>
       </c>
       <c r="T67">
-        <v>1.520318271584431</v>
+        <v>1.565033514866326</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.2116038972485265</v>
+        <v>0.2083977775932458</v>
       </c>
       <c r="W67">
-        <v>0.1157365478839163</v>
+        <v>0.1162072062493115</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8464155889941058</v>
+        <v>0.8335911103729831</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1266658042581426</v>
+        <v>0.1276758042581426</v>
       </c>
       <c r="C68">
-        <v>-632.9238611696092</v>
+        <v>-693.1083338122246</v>
       </c>
       <c r="D68">
-        <v>1801.468138830391</v>
+        <v>1779.245666187776</v>
       </c>
       <c r="E68">
-        <v>1922.092</v>
+        <v>1960.054</v>
       </c>
       <c r="F68">
-        <v>2505.492</v>
+        <v>2543.454</v>
       </c>
       <c r="G68">
         <v>71.09999999999999</v>
@@ -6863,37 +6863,37 @@
         <v>306.6</v>
       </c>
       <c r="M68">
-        <v>367.8062256000001</v>
+        <v>373.3790472000001</v>
       </c>
       <c r="N68">
-        <v>-61.2062256000001</v>
+        <v>-66.77904720000009</v>
       </c>
       <c r="O68">
-        <v>-15.30155640000002</v>
+        <v>-16.69476180000002</v>
       </c>
       <c r="P68">
-        <v>-45.90466920000007</v>
+        <v>-50.08428540000007</v>
       </c>
       <c r="Q68">
-        <v>74.39533079999993</v>
+        <v>70.21571459999993</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1469677886282263</v>
+        <v>0.150033479192718</v>
       </c>
       <c r="T68">
-        <v>1.565033514866326</v>
+        <v>1.612458772892578</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.2083977775932458</v>
+        <v>0.2052873630023018</v>
       </c>
       <c r="W68">
-        <v>0.1162072062493115</v>
+        <v>0.1166638151112621</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8335911103729831</v>
+        <v>0.8211494520092072</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1276758042581426</v>
+        <v>0.1286858042581425</v>
       </c>
       <c r="C69">
-        <v>-693.1083338122246</v>
+        <v>-752.7512252378888</v>
       </c>
       <c r="D69">
-        <v>1779.245666187776</v>
+        <v>1757.564774762111</v>
       </c>
       <c r="E69">
-        <v>1960.054</v>
+        <v>1998.016</v>
       </c>
       <c r="F69">
-        <v>2543.454</v>
+        <v>2581.416</v>
       </c>
       <c r="G69">
         <v>71.09999999999999</v>
@@ -6945,37 +6945,37 @@
         <v>306.6</v>
       </c>
       <c r="M69">
-        <v>373.3790472000001</v>
+        <v>378.9518688000001</v>
       </c>
       <c r="N69">
-        <v>-66.77904720000009</v>
+        <v>-72.35186880000009</v>
       </c>
       <c r="O69">
-        <v>-16.69476180000002</v>
+        <v>-18.08796720000002</v>
       </c>
       <c r="P69">
-        <v>-50.08428540000007</v>
+        <v>-54.26390160000007</v>
       </c>
       <c r="Q69">
-        <v>70.21571459999993</v>
+        <v>66.03609839999993</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.150033479192718</v>
+        <v>0.1532907754174904</v>
       </c>
       <c r="T69">
-        <v>1.612458772892578</v>
+        <v>1.662848109545471</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.2052873630023018</v>
+        <v>0.2022684311934444</v>
       </c>
       <c r="W69">
-        <v>0.1166638151112621</v>
+        <v>0.1171069943008024</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8211494520092072</v>
+        <v>0.8090737247737777</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1286858042581425</v>
+        <v>0.1684310030830781</v>
       </c>
       <c r="C70">
-        <v>-752.7512252378888</v>
+        <v>-1360.347001888147</v>
       </c>
       <c r="D70">
-        <v>1757.564774762111</v>
+        <v>1187.930998111854</v>
       </c>
       <c r="E70">
-        <v>1998.016</v>
+        <v>2035.978000000001</v>
       </c>
       <c r="F70">
-        <v>2581.416</v>
+        <v>2619.378000000001</v>
       </c>
       <c r="G70">
         <v>71.09999999999999</v>
@@ -7027,45 +7027,45 @@
         <v>306.6</v>
       </c>
       <c r="M70">
-        <v>378.9518688000001</v>
+        <v>525.9711024000002</v>
       </c>
       <c r="N70">
-        <v>-72.35186880000009</v>
+        <v>-219.3711024000002</v>
       </c>
       <c r="O70">
-        <v>-18.08796720000002</v>
+        <v>-54.84277560000005</v>
       </c>
       <c r="P70">
-        <v>-54.26390160000007</v>
+        <v>-164.5283268000002</v>
       </c>
       <c r="Q70">
-        <v>66.03609839999993</v>
+        <v>-44.22832680000018</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1532907754174904</v>
+        <v>0.1615169256726854</v>
       </c>
       <c r="T70">
-        <v>1.662848109545471</v>
+        <v>1.790104037764053</v>
       </c>
       <c r="U70">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.2022684311934444</v>
+        <v>0.1457304396577054</v>
       </c>
       <c r="W70">
-        <v>0.1171069943008024</v>
+        <v>0.1715373277167328</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.8090737247737777</v>
+        <v>0.5829217586308214</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1684310030830781</v>
+        <v>0.1699810030830781</v>
       </c>
       <c r="C71">
-        <v>-1360.347001888147</v>
+        <v>-1413.136495638069</v>
       </c>
       <c r="D71">
-        <v>1187.930998111854</v>
+        <v>1173.103504361932</v>
       </c>
       <c r="E71">
-        <v>2035.978000000001</v>
+        <v>2073.940000000001</v>
       </c>
       <c r="F71">
-        <v>2619.378000000001</v>
+        <v>2657.340000000001</v>
       </c>
       <c r="G71">
         <v>71.09999999999999</v>
@@ -7109,37 +7109,37 @@
         <v>306.6</v>
       </c>
       <c r="M71">
-        <v>525.9711024000002</v>
+        <v>533.5938720000001</v>
       </c>
       <c r="N71">
-        <v>-219.3711024000002</v>
+        <v>-226.9938720000002</v>
       </c>
       <c r="O71">
-        <v>-54.84277560000005</v>
+        <v>-56.74846800000005</v>
       </c>
       <c r="P71">
-        <v>-164.5283268000002</v>
+        <v>-170.2454040000001</v>
       </c>
       <c r="Q71">
-        <v>-44.22832680000018</v>
+        <v>-49.94540400000012</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1615169256726854</v>
+        <v>0.1653741565284416</v>
       </c>
       <c r="T71">
-        <v>1.790104037764053</v>
+        <v>1.849774172356188</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1457304396577054</v>
+        <v>0.1436485762340239</v>
       </c>
       <c r="W71">
-        <v>0.1715373277167328</v>
+        <v>0.171955365892208</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5829217586308214</v>
+        <v>0.5745943049360954</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1699810030830781</v>
+        <v>0.1715310030830781</v>
       </c>
       <c r="C72">
-        <v>-1413.136495638069</v>
+        <v>-1465.560405486665</v>
       </c>
       <c r="D72">
-        <v>1173.103504361932</v>
+        <v>1158.641594513336</v>
       </c>
       <c r="E72">
-        <v>2073.940000000001</v>
+        <v>2111.902</v>
       </c>
       <c r="F72">
-        <v>2657.340000000001</v>
+        <v>2695.302000000001</v>
       </c>
       <c r="G72">
         <v>71.09999999999999</v>
@@ -7191,37 +7191,37 @@
         <v>306.6</v>
       </c>
       <c r="M72">
-        <v>533.5938720000001</v>
+        <v>541.2166416000001</v>
       </c>
       <c r="N72">
-        <v>-226.9938720000002</v>
+        <v>-234.6166416000002</v>
       </c>
       <c r="O72">
-        <v>-56.74846800000005</v>
+        <v>-58.65416040000004</v>
       </c>
       <c r="P72">
-        <v>-170.2454040000001</v>
+        <v>-175.9624812000001</v>
       </c>
       <c r="Q72">
-        <v>-49.94540400000012</v>
+        <v>-55.66248120000013</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1653741565284416</v>
+        <v>0.1694974033052844</v>
       </c>
       <c r="T72">
-        <v>1.849774172356188</v>
+        <v>1.913559488644333</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1436485762340239</v>
+        <v>0.1416253568504461</v>
       </c>
       <c r="W72">
-        <v>0.171955365892208</v>
+        <v>0.1723616283444304</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5745943049360954</v>
+        <v>0.5665014274017843</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1715310030830781</v>
+        <v>0.1730810030830781</v>
       </c>
       <c r="C73">
-        <v>-1465.560405486664</v>
+        <v>-1517.632087434436</v>
       </c>
       <c r="D73">
-        <v>1158.641594513336</v>
+        <v>1144.531912565564</v>
       </c>
       <c r="E73">
-        <v>2111.902</v>
+        <v>2149.864</v>
       </c>
       <c r="F73">
-        <v>2695.302</v>
+        <v>2733.264</v>
       </c>
       <c r="G73">
         <v>71.09999999999999</v>
@@ -7273,37 +7273,37 @@
         <v>306.6</v>
       </c>
       <c r="M73">
-        <v>541.2166416</v>
+        <v>548.8394112000001</v>
       </c>
       <c r="N73">
-        <v>-234.6166416</v>
+        <v>-242.2394112000001</v>
       </c>
       <c r="O73">
-        <v>-58.65416040000001</v>
+        <v>-60.55985280000003</v>
       </c>
       <c r="P73">
-        <v>-175.9624812</v>
+        <v>-181.6795584000001</v>
       </c>
       <c r="Q73">
-        <v>-55.66248120000002</v>
+        <v>-61.37955840000008</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1694974033052843</v>
+        <v>0.1739151677090445</v>
       </c>
       <c r="T73">
-        <v>1.913559488644332</v>
+        <v>1.981900898953058</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1416253568504461</v>
+        <v>0.139658338005301</v>
       </c>
       <c r="W73">
-        <v>0.1723616283444304</v>
+        <v>0.1727566057285355</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5665014274017843</v>
+        <v>0.5586333520212039</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1730810030830781</v>
+        <v>0.1746310030830781</v>
       </c>
       <c r="C74">
-        <v>-1517.632087434436</v>
+        <v>-1569.364254723537</v>
       </c>
       <c r="D74">
-        <v>1144.531912565564</v>
+        <v>1130.761745276463</v>
       </c>
       <c r="E74">
-        <v>2149.864</v>
+        <v>2187.826</v>
       </c>
       <c r="F74">
-        <v>2733.264</v>
+        <v>2771.226</v>
       </c>
       <c r="G74">
         <v>71.09999999999999</v>
@@ -7355,37 +7355,37 @@
         <v>306.6</v>
       </c>
       <c r="M74">
-        <v>548.8394112000001</v>
+        <v>556.4621808000001</v>
       </c>
       <c r="N74">
-        <v>-242.2394112000001</v>
+        <v>-249.8621808000001</v>
       </c>
       <c r="O74">
-        <v>-60.55985280000003</v>
+        <v>-62.46554520000002</v>
       </c>
       <c r="P74">
-        <v>-181.6795584000001</v>
+        <v>-187.3966356000001</v>
       </c>
       <c r="Q74">
-        <v>-61.37955840000008</v>
+        <v>-67.09663560000008</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1739151677090445</v>
+        <v>0.1786601739204906</v>
       </c>
       <c r="T74">
-        <v>1.981900898953058</v>
+        <v>2.05530463595132</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.139658338005301</v>
+        <v>0.1377452100874202</v>
       </c>
       <c r="W74">
-        <v>0.1727566057285355</v>
+        <v>0.173140761814446</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5586333520212039</v>
+        <v>0.5509808403496806</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1746310030830781</v>
+        <v>0.176181003083078</v>
       </c>
       <c r="C75">
-        <v>-1569.364254723537</v>
+        <v>-1620.769016044078</v>
       </c>
       <c r="D75">
-        <v>1130.761745276463</v>
+        <v>1117.318983955922</v>
       </c>
       <c r="E75">
-        <v>2187.826</v>
+        <v>2225.788</v>
       </c>
       <c r="F75">
-        <v>2771.226</v>
+        <v>2809.188</v>
       </c>
       <c r="G75">
         <v>71.09999999999999</v>
@@ -7437,37 +7437,37 @@
         <v>306.6</v>
       </c>
       <c r="M75">
-        <v>556.4621808000001</v>
+        <v>564.0849504</v>
       </c>
       <c r="N75">
-        <v>-249.8621808000001</v>
+        <v>-257.4849504000001</v>
       </c>
       <c r="O75">
-        <v>-62.46554520000002</v>
+        <v>-64.37123760000001</v>
       </c>
       <c r="P75">
-        <v>-187.3966356000001</v>
+        <v>-193.1137128</v>
       </c>
       <c r="Q75">
-        <v>-67.09663560000008</v>
+        <v>-72.81371280000003</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1786601739204906</v>
+        <v>0.1837701806097402</v>
       </c>
       <c r="T75">
-        <v>2.05530463595132</v>
+        <v>2.13435481425714</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1377452100874202</v>
+        <v>0.1358837883294821</v>
       </c>
       <c r="W75">
-        <v>0.173140761814446</v>
+        <v>0.17351453530344</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5509808403496806</v>
+        <v>0.5435351533179282</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.176181003083078</v>
+        <v>0.1777310030830781</v>
       </c>
       <c r="C76">
-        <v>-1620.769016044078</v>
+        <v>-1671.857911047227</v>
       </c>
       <c r="D76">
-        <v>1117.318983955922</v>
+        <v>1104.192088952773</v>
       </c>
       <c r="E76">
-        <v>2225.788</v>
+        <v>2263.75</v>
       </c>
       <c r="F76">
-        <v>2809.188</v>
+        <v>2847.15</v>
       </c>
       <c r="G76">
         <v>71.09999999999999</v>
@@ -7519,37 +7519,37 @@
         <v>306.6</v>
       </c>
       <c r="M76">
-        <v>564.0849504</v>
+        <v>571.70772</v>
       </c>
       <c r="N76">
-        <v>-257.4849504000001</v>
+        <v>-265.10772</v>
       </c>
       <c r="O76">
-        <v>-64.37123760000001</v>
+        <v>-66.27693000000001</v>
       </c>
       <c r="P76">
-        <v>-193.1137128</v>
+        <v>-198.83079</v>
       </c>
       <c r="Q76">
-        <v>-72.81371280000003</v>
+        <v>-78.53079000000004</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1837701806097402</v>
+        <v>0.1892889878341299</v>
       </c>
       <c r="T76">
-        <v>2.13435481425714</v>
+        <v>2.219729006827425</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1358837883294821</v>
+        <v>0.134072004485089</v>
       </c>
       <c r="W76">
-        <v>0.17351453530344</v>
+        <v>0.1738783414993942</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5435351533179282</v>
+        <v>0.536288017940356</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1777310030830781</v>
+        <v>0.1792810030830781</v>
       </c>
       <c r="C77">
-        <v>-1671.857911047227</v>
+        <v>-1722.641943384005</v>
       </c>
       <c r="D77">
-        <v>1104.192088952773</v>
+        <v>1091.370056615995</v>
       </c>
       <c r="E77">
-        <v>2263.75</v>
+        <v>2301.712</v>
       </c>
       <c r="F77">
-        <v>2847.15</v>
+        <v>2885.112</v>
       </c>
       <c r="G77">
         <v>71.09999999999999</v>
@@ -7601,37 +7601,37 @@
         <v>306.6</v>
       </c>
       <c r="M77">
-        <v>571.70772</v>
+        <v>579.3304896000001</v>
       </c>
       <c r="N77">
-        <v>-265.10772</v>
+        <v>-272.7304896000001</v>
       </c>
       <c r="O77">
-        <v>-66.27693000000001</v>
+        <v>-68.18262240000003</v>
       </c>
       <c r="P77">
-        <v>-198.83079</v>
+        <v>-204.5478672000001</v>
       </c>
       <c r="Q77">
-        <v>-78.53079000000004</v>
+        <v>-84.2478672000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1892889878341299</v>
+        <v>0.195267695660552</v>
       </c>
       <c r="T77">
-        <v>2.219729006827425</v>
+        <v>2.312217715445235</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.134072004485089</v>
+        <v>0.1323078991629167</v>
       </c>
       <c r="W77">
-        <v>0.1738783414993942</v>
+        <v>0.1742325738480863</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.536288017940356</v>
+        <v>0.529231596651667</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1792810030830781</v>
+        <v>0.1808310030830781</v>
       </c>
       <c r="C78">
-        <v>-1722.641943384005</v>
+        <v>-1773.1316114686</v>
       </c>
       <c r="D78">
-        <v>1091.370056615995</v>
+        <v>1078.8423885314</v>
       </c>
       <c r="E78">
-        <v>2301.712</v>
+        <v>2339.674</v>
       </c>
       <c r="F78">
-        <v>2885.112</v>
+        <v>2923.074</v>
       </c>
       <c r="G78">
         <v>71.09999999999999</v>
@@ -7683,37 +7683,37 @@
         <v>306.6</v>
       </c>
       <c r="M78">
-        <v>579.3304896000001</v>
+        <v>586.9532592</v>
       </c>
       <c r="N78">
-        <v>-272.7304896000001</v>
+        <v>-280.3532592000001</v>
       </c>
       <c r="O78">
-        <v>-68.18262240000003</v>
+        <v>-70.08831480000002</v>
       </c>
       <c r="P78">
-        <v>-204.5478672000001</v>
+        <v>-210.2649444</v>
       </c>
       <c r="Q78">
-        <v>-84.2478672000001</v>
+        <v>-89.96494440000005</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.195267695660552</v>
+        <v>0.2017662911240542</v>
       </c>
       <c r="T78">
-        <v>2.312217715445235</v>
+        <v>2.412748920464593</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1323078991629167</v>
+        <v>0.1305896147582035</v>
       </c>
       <c r="W78">
-        <v>0.1742325738480863</v>
+        <v>0.1745776053565527</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.529231596651667</v>
+        <v>0.5223584590328141</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1808310030830781</v>
+        <v>0.1823810030830781</v>
       </c>
       <c r="C79">
-        <v>-1773.1316114686</v>
+        <v>-1823.336937146964</v>
       </c>
       <c r="D79">
-        <v>1078.8423885314</v>
+        <v>1066.599062853037</v>
       </c>
       <c r="E79">
-        <v>2339.674</v>
+        <v>2377.636</v>
       </c>
       <c r="F79">
-        <v>2923.074</v>
+        <v>2961.036000000001</v>
       </c>
       <c r="G79">
         <v>71.09999999999999</v>
@@ -7765,37 +7765,37 @@
         <v>306.6</v>
       </c>
       <c r="M79">
-        <v>586.9532592</v>
+        <v>594.5760288000001</v>
       </c>
       <c r="N79">
-        <v>-280.3532592000001</v>
+        <v>-287.9760288000002</v>
       </c>
       <c r="O79">
-        <v>-70.08831480000002</v>
+        <v>-71.99400720000004</v>
       </c>
       <c r="P79">
-        <v>-210.2649444</v>
+        <v>-215.9820216000001</v>
       </c>
       <c r="Q79">
-        <v>-89.96494440000005</v>
+        <v>-95.68202160000011</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2017662911240542</v>
+        <v>0.2088556679933294</v>
       </c>
       <c r="T79">
-        <v>2.412748920464593</v>
+        <v>2.522419325940256</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1305896147582035</v>
+        <v>0.1289153889279701</v>
       </c>
       <c r="W79">
-        <v>0.1745776053565527</v>
+        <v>0.1749137899032636</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5223584590328141</v>
+        <v>0.5156615557118805</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1823810030830781</v>
+        <v>0.1839310030830781</v>
       </c>
       <c r="C80">
-        <v>-1823.336937146964</v>
+        <v>-1873.267492435221</v>
       </c>
       <c r="D80">
-        <v>1066.599062853037</v>
+        <v>1054.63050756478</v>
       </c>
       <c r="E80">
-        <v>2377.636</v>
+        <v>2415.598</v>
       </c>
       <c r="F80">
-        <v>2961.036000000001</v>
+        <v>2998.998000000001</v>
       </c>
       <c r="G80">
         <v>71.09999999999999</v>
@@ -7847,37 +7847,37 @@
         <v>306.6</v>
       </c>
       <c r="M80">
-        <v>594.5760288000001</v>
+        <v>602.1987984000001</v>
       </c>
       <c r="N80">
-        <v>-287.9760288000002</v>
+        <v>-295.5987984000001</v>
       </c>
       <c r="O80">
-        <v>-71.99400720000004</v>
+        <v>-73.89969960000003</v>
       </c>
       <c r="P80">
-        <v>-215.9820216000001</v>
+        <v>-221.6990988000001</v>
       </c>
       <c r="Q80">
-        <v>-95.68202160000011</v>
+        <v>-101.3990988000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2088556679933294</v>
+        <v>0.2166202236120594</v>
       </c>
       <c r="T80">
-        <v>2.522419325940256</v>
+        <v>2.642534531937412</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1289153889279701</v>
+        <v>0.1272835485617933</v>
       </c>
       <c r="W80">
-        <v>0.1749137899032636</v>
+        <v>0.1752414634487919</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5156615557118805</v>
+        <v>0.5091341942471732</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1839310030830781</v>
+        <v>0.1854810030830781</v>
       </c>
       <c r="C81">
-        <v>-1873.267492435221</v>
+        <v>-1922.932424477835</v>
       </c>
       <c r="D81">
-        <v>1054.63050756478</v>
+        <v>1042.927575522166</v>
       </c>
       <c r="E81">
-        <v>2415.598</v>
+        <v>2453.56</v>
       </c>
       <c r="F81">
-        <v>2998.998000000001</v>
+        <v>3036.96</v>
       </c>
       <c r="G81">
         <v>71.09999999999999</v>
@@ -7929,37 +7929,37 @@
         <v>306.6</v>
       </c>
       <c r="M81">
-        <v>602.1987984000001</v>
+        <v>609.8215680000001</v>
       </c>
       <c r="N81">
-        <v>-295.5987984000001</v>
+        <v>-303.2215680000001</v>
       </c>
       <c r="O81">
-        <v>-73.89969960000003</v>
+        <v>-75.80539200000003</v>
       </c>
       <c r="P81">
-        <v>-221.6990988000001</v>
+        <v>-227.4161760000001</v>
       </c>
       <c r="Q81">
-        <v>-101.3990988000001</v>
+        <v>-107.1161760000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2166202236120594</v>
+        <v>0.2251612347926623</v>
       </c>
       <c r="T81">
-        <v>2.642534531937412</v>
+        <v>2.774661258534282</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1272835485617933</v>
+        <v>0.1256925042047709</v>
       </c>
       <c r="W81">
-        <v>0.1752414634487919</v>
+        <v>0.175560945155682</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5091341942471732</v>
+        <v>0.5027700168190836</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1854810030830781</v>
+        <v>0.2159762636273653</v>
       </c>
       <c r="C82">
-        <v>-1922.932424477835</v>
+        <v>-2147.785048742639</v>
       </c>
       <c r="D82">
-        <v>1042.927575522166</v>
+        <v>856.0369512573612</v>
       </c>
       <c r="E82">
-        <v>2453.56</v>
+        <v>2491.522</v>
       </c>
       <c r="F82">
-        <v>3036.96</v>
+        <v>3074.922</v>
       </c>
       <c r="G82">
         <v>71.09999999999999</v>
@@ -8011,45 +8011,45 @@
         <v>306.6</v>
       </c>
       <c r="M82">
-        <v>609.8215680000001</v>
+        <v>725.0666076000001</v>
       </c>
       <c r="N82">
-        <v>-303.2215680000001</v>
+        <v>-418.4666076000001</v>
       </c>
       <c r="O82">
-        <v>-75.80539200000003</v>
+        <v>-104.6166519</v>
       </c>
       <c r="P82">
-        <v>-227.4161760000001</v>
+        <v>-313.8499557000001</v>
       </c>
       <c r="Q82">
-        <v>-107.1161760000001</v>
+        <v>-193.5499557000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2251612347926623</v>
+        <v>0.2377342500148408</v>
       </c>
       <c r="T82">
-        <v>2.774661258534282</v>
+        <v>2.969161805323378</v>
       </c>
       <c r="U82">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1256925042047709</v>
+        <v>0.1057144256769935</v>
       </c>
       <c r="W82">
-        <v>0.175560945155682</v>
+        <v>0.2108725384253649</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.5027700168190836</v>
+        <v>0.4228577027079738</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2159762636273653</v>
+        <v>0.2178762636273654</v>
       </c>
       <c r="C83">
-        <v>-2147.785048742639</v>
+        <v>-2195.199079912442</v>
       </c>
       <c r="D83">
-        <v>856.0369512573612</v>
+        <v>846.5849200875585</v>
       </c>
       <c r="E83">
-        <v>2491.522</v>
+        <v>2529.484</v>
       </c>
       <c r="F83">
-        <v>3074.922</v>
+        <v>3112.884</v>
       </c>
       <c r="G83">
         <v>71.09999999999999</v>
@@ -8093,37 +8093,37 @@
         <v>306.6</v>
       </c>
       <c r="M83">
-        <v>725.0666076000001</v>
+        <v>734.0180472000002</v>
       </c>
       <c r="N83">
-        <v>-418.4666076000001</v>
+        <v>-427.4180472000002</v>
       </c>
       <c r="O83">
-        <v>-104.6166519</v>
+        <v>-106.8545118000001</v>
       </c>
       <c r="P83">
-        <v>-313.8499557000001</v>
+        <v>-320.5635354000001</v>
       </c>
       <c r="Q83">
-        <v>-193.5499557000001</v>
+        <v>-200.2635354000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2377342500148408</v>
+        <v>0.2483972639045542</v>
       </c>
       <c r="T83">
-        <v>2.969161805323378</v>
+        <v>3.134115238952455</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1057144256769935</v>
+        <v>0.1044252253638594</v>
       </c>
       <c r="W83">
-        <v>0.2108725384253649</v>
+        <v>0.211176531859202</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4228577027079738</v>
+        <v>0.4177009014554375</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2178762636273654</v>
+        <v>0.2197762636273654</v>
       </c>
       <c r="C84">
-        <v>-2195.199079912442</v>
+        <v>-2242.406659249699</v>
       </c>
       <c r="D84">
-        <v>846.5849200875585</v>
+        <v>837.3393407503017</v>
       </c>
       <c r="E84">
-        <v>2529.484</v>
+        <v>2567.446</v>
       </c>
       <c r="F84">
-        <v>3112.884</v>
+        <v>3150.846</v>
       </c>
       <c r="G84">
         <v>71.09999999999999</v>
@@ -8175,37 +8175,37 @@
         <v>306.6</v>
       </c>
       <c r="M84">
-        <v>734.0180472000002</v>
+        <v>742.9694868000001</v>
       </c>
       <c r="N84">
-        <v>-427.4180472000002</v>
+        <v>-436.3694868000002</v>
       </c>
       <c r="O84">
-        <v>-106.8545118000001</v>
+        <v>-109.0923717</v>
       </c>
       <c r="P84">
-        <v>-320.5635354000001</v>
+        <v>-327.2771151000001</v>
       </c>
       <c r="Q84">
-        <v>-200.2635354000001</v>
+        <v>-206.9771151000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2483972639045542</v>
+        <v>0.2603147500165868</v>
       </c>
       <c r="T84">
-        <v>3.134115238952455</v>
+        <v>3.318474958890835</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1044252253638594</v>
+        <v>0.1031670901185117</v>
       </c>
       <c r="W84">
-        <v>0.211176531859202</v>
+        <v>0.211473200150055</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4177009014554375</v>
+        <v>0.4126683604740468</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2197762636273654</v>
+        <v>0.2216762636273654</v>
       </c>
       <c r="C85">
-        <v>-2242.406659249699</v>
+        <v>-2289.414477682574</v>
       </c>
       <c r="D85">
-        <v>837.3393407503017</v>
+        <v>828.2935223174266</v>
       </c>
       <c r="E85">
-        <v>2567.446</v>
+        <v>2605.408</v>
       </c>
       <c r="F85">
-        <v>3150.846</v>
+        <v>3188.808</v>
       </c>
       <c r="G85">
         <v>71.09999999999999</v>
@@ -8257,37 +8257,37 @@
         <v>306.6</v>
       </c>
       <c r="M85">
-        <v>742.9694868000001</v>
+        <v>751.9209264000001</v>
       </c>
       <c r="N85">
-        <v>-436.3694868000002</v>
+        <v>-445.3209264000001</v>
       </c>
       <c r="O85">
-        <v>-109.0923717</v>
+        <v>-111.3302316</v>
       </c>
       <c r="P85">
-        <v>-327.2771151000001</v>
+        <v>-333.9906948000001</v>
       </c>
       <c r="Q85">
-        <v>-206.9771151000001</v>
+        <v>-213.6906948000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2603147500165868</v>
+        <v>0.2737219218926235</v>
       </c>
       <c r="T85">
-        <v>3.318474958890835</v>
+        <v>3.525879643821513</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1031670901185117</v>
+        <v>0.1019389104742437</v>
       </c>
       <c r="W85">
-        <v>0.211473200150055</v>
+        <v>0.2117628049101734</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4126683604740468</v>
+        <v>0.4077556418969748</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2216762636273653</v>
+        <v>0.2235762636273654</v>
       </c>
       <c r="C86">
-        <v>-2289.414477682573</v>
+        <v>-2336.228940099613</v>
       </c>
       <c r="D86">
-        <v>828.293522317427</v>
+        <v>819.4410599003866</v>
       </c>
       <c r="E86">
-        <v>2605.408</v>
+        <v>2643.37</v>
       </c>
       <c r="F86">
-        <v>3188.808</v>
+        <v>3226.77</v>
       </c>
       <c r="G86">
         <v>71.09999999999999</v>
@@ -8339,37 +8339,37 @@
         <v>306.6</v>
       </c>
       <c r="M86">
-        <v>751.9209264</v>
+        <v>760.8723660000001</v>
       </c>
       <c r="N86">
-        <v>-445.3209264</v>
+        <v>-454.2723660000001</v>
       </c>
       <c r="O86">
-        <v>-111.3302316</v>
+        <v>-113.5680915</v>
       </c>
       <c r="P86">
-        <v>-333.9906948</v>
+        <v>-340.7042745000001</v>
       </c>
       <c r="Q86">
-        <v>-213.6906948</v>
+        <v>-220.4042745</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2737219218926233</v>
+        <v>0.2889167166854649</v>
       </c>
       <c r="T86">
-        <v>3.525879643821511</v>
+        <v>3.760938286742945</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1019389104742437</v>
+        <v>0.1007396291745467</v>
       </c>
       <c r="W86">
-        <v>0.2117628049101733</v>
+        <v>0.2120455954406419</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4077556418969749</v>
+        <v>0.4029585166981868</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2235762636273654</v>
+        <v>0.2254762636273654</v>
       </c>
       <c r="C87">
-        <v>-2336.228940099613</v>
+        <v>-2382.856180473488</v>
       </c>
       <c r="D87">
-        <v>819.4410599003866</v>
+        <v>810.7758195265122</v>
       </c>
       <c r="E87">
-        <v>2643.37</v>
+        <v>2681.332</v>
       </c>
       <c r="F87">
-        <v>3226.77</v>
+        <v>3264.732</v>
       </c>
       <c r="G87">
         <v>71.09999999999999</v>
@@ -8421,37 +8421,37 @@
         <v>306.6</v>
       </c>
       <c r="M87">
-        <v>760.8723660000001</v>
+        <v>769.8238056</v>
       </c>
       <c r="N87">
-        <v>-454.2723660000001</v>
+        <v>-463.2238056</v>
       </c>
       <c r="O87">
-        <v>-113.5680915</v>
+        <v>-115.8059514</v>
       </c>
       <c r="P87">
-        <v>-340.7042745000001</v>
+        <v>-347.4178542</v>
       </c>
       <c r="Q87">
-        <v>-220.4042745</v>
+        <v>-227.1178542</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2889167166854649</v>
+        <v>0.3062821964487124</v>
       </c>
       <c r="T87">
-        <v>3.760938286742945</v>
+        <v>4.029576735796012</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1007396291745467</v>
+        <v>0.09956823813763338</v>
       </c>
       <c r="W87">
-        <v>0.2120455954406419</v>
+        <v>0.2123218094471461</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4029585166981868</v>
+        <v>0.3982729525505335</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2254762636273654</v>
+        <v>0.2273762636273653</v>
       </c>
       <c r="C88">
-        <v>-2382.856180473488</v>
+        <v>-2429.3020760352</v>
       </c>
       <c r="D88">
-        <v>810.7758195265122</v>
+        <v>802.2919239648004</v>
       </c>
       <c r="E88">
-        <v>2681.332</v>
+        <v>2719.294</v>
       </c>
       <c r="F88">
-        <v>3264.732</v>
+        <v>3302.694</v>
       </c>
       <c r="G88">
         <v>71.09999999999999</v>
@@ -8503,37 +8503,37 @@
         <v>306.6</v>
       </c>
       <c r="M88">
-        <v>769.8238056</v>
+        <v>778.7752452000001</v>
       </c>
       <c r="N88">
-        <v>-463.2238056</v>
+        <v>-472.1752452000001</v>
       </c>
       <c r="O88">
-        <v>-115.8059514</v>
+        <v>-118.0438113</v>
       </c>
       <c r="P88">
-        <v>-347.4178542</v>
+        <v>-354.1314339000001</v>
       </c>
       <c r="Q88">
-        <v>-227.1178542</v>
+        <v>-233.8314339000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3062821964487124</v>
+        <v>0.3263192884832288</v>
       </c>
       <c r="T88">
-        <v>4.029576735796012</v>
+        <v>4.33954417701109</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.09956823813763338</v>
+        <v>0.09842377563030426</v>
       </c>
       <c r="W88">
-        <v>0.2123218094471461</v>
+        <v>0.2125916737063743</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3982729525505335</v>
+        <v>0.393695102521217</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2273762636273653</v>
+        <v>0.2292762636273653</v>
       </c>
       <c r="C89">
-        <v>-2429.3020760352</v>
+        <v>-2475.572260567609</v>
       </c>
       <c r="D89">
-        <v>802.2919239648004</v>
+        <v>793.9837394323915</v>
       </c>
       <c r="E89">
-        <v>2719.294</v>
+        <v>2757.256</v>
       </c>
       <c r="F89">
-        <v>3302.694</v>
+        <v>3340.656</v>
       </c>
       <c r="G89">
         <v>71.09999999999999</v>
@@ -8585,37 +8585,37 @@
         <v>306.6</v>
       </c>
       <c r="M89">
-        <v>778.7752452000001</v>
+        <v>787.7266848000002</v>
       </c>
       <c r="N89">
-        <v>-472.1752452000001</v>
+        <v>-481.1266848000002</v>
       </c>
       <c r="O89">
-        <v>-118.0438113</v>
+        <v>-120.2816712</v>
       </c>
       <c r="P89">
-        <v>-354.1314339000001</v>
+        <v>-360.8450136000001</v>
       </c>
       <c r="Q89">
-        <v>-233.8314339000001</v>
+        <v>-240.5450136000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3263192884832288</v>
+        <v>0.3496958958568312</v>
       </c>
       <c r="T89">
-        <v>4.33954417701109</v>
+        <v>4.701172858428682</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.09842377563030426</v>
+        <v>0.09730532363450534</v>
       </c>
       <c r="W89">
-        <v>0.2125916737063743</v>
+        <v>0.2128554046869836</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.393695102521217</v>
+        <v>0.3892212945380213</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2292762636273653</v>
+        <v>0.2311762636273654</v>
       </c>
       <c r="C90">
-        <v>-2475.572260567609</v>
+        <v>-2521.672136881451</v>
       </c>
       <c r="D90">
-        <v>793.9837394323915</v>
+        <v>785.8458631185497</v>
       </c>
       <c r="E90">
-        <v>2757.256</v>
+        <v>2795.218</v>
       </c>
       <c r="F90">
-        <v>3340.656</v>
+        <v>3378.618</v>
       </c>
       <c r="G90">
         <v>71.09999999999999</v>
@@ -8667,37 +8667,37 @@
         <v>306.6</v>
       </c>
       <c r="M90">
-        <v>787.7266848000002</v>
+        <v>796.6781244000001</v>
       </c>
       <c r="N90">
-        <v>-481.1266848000002</v>
+        <v>-490.0781244000001</v>
       </c>
       <c r="O90">
-        <v>-120.2816712</v>
+        <v>-122.5195311</v>
       </c>
       <c r="P90">
-        <v>-360.8450136000001</v>
+        <v>-367.5585933000001</v>
       </c>
       <c r="Q90">
-        <v>-240.5450136000001</v>
+        <v>-247.2585933000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3496958958568312</v>
+        <v>0.3773227954801795</v>
       </c>
       <c r="T90">
-        <v>4.701172858428682</v>
+        <v>5.128552209194925</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.09730532363450534</v>
+        <v>0.09621200539142101</v>
       </c>
       <c r="W90">
-        <v>0.2128554046869836</v>
+        <v>0.2131132091287029</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3892212945380213</v>
+        <v>0.3848480215656841</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2311762636273654</v>
+        <v>0.2330762636273653</v>
       </c>
       <c r="C91">
-        <v>-2521.672136881451</v>
+        <v>-2567.606888531901</v>
       </c>
       <c r="D91">
-        <v>785.8458631185497</v>
+        <v>777.8731114680996</v>
       </c>
       <c r="E91">
-        <v>2795.218</v>
+        <v>2833.18</v>
       </c>
       <c r="F91">
-        <v>3378.618</v>
+        <v>3416.58</v>
       </c>
       <c r="G91">
         <v>71.09999999999999</v>
@@ -8749,37 +8749,37 @@
         <v>306.6</v>
       </c>
       <c r="M91">
-        <v>796.6781244000001</v>
+        <v>805.6295640000001</v>
       </c>
       <c r="N91">
-        <v>-490.0781244000001</v>
+        <v>-499.0295640000001</v>
       </c>
       <c r="O91">
-        <v>-122.5195311</v>
+        <v>-124.757391</v>
       </c>
       <c r="P91">
-        <v>-367.5585933000001</v>
+        <v>-374.2721730000001</v>
       </c>
       <c r="Q91">
-        <v>-247.2585933000001</v>
+        <v>-253.9721730000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3773227954801795</v>
+        <v>0.4104750750281975</v>
       </c>
       <c r="T91">
-        <v>5.128552209194925</v>
+        <v>5.641407430114419</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.09621200539142101</v>
+        <v>0.09514298310929412</v>
       </c>
       <c r="W91">
-        <v>0.2131132091287029</v>
+        <v>0.2133652845828284</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3848480215656841</v>
+        <v>0.3805719324371765</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2330762636273653</v>
+        <v>0.2349762636273653</v>
       </c>
       <c r="C92">
-        <v>-2567.606888531901</v>
+        <v>-2613.381490829093</v>
       </c>
       <c r="D92">
-        <v>777.8731114680996</v>
+        <v>770.0605091709076</v>
       </c>
       <c r="E92">
-        <v>2833.18</v>
+        <v>2871.142</v>
       </c>
       <c r="F92">
-        <v>3416.58</v>
+        <v>3454.542</v>
       </c>
       <c r="G92">
         <v>71.09999999999999</v>
@@ -8831,37 +8831,37 @@
         <v>306.6</v>
       </c>
       <c r="M92">
-        <v>805.6295640000001</v>
+        <v>814.5810036000001</v>
       </c>
       <c r="N92">
-        <v>-499.0295640000001</v>
+        <v>-507.9810036000002</v>
       </c>
       <c r="O92">
-        <v>-124.757391</v>
+        <v>-126.9952509</v>
       </c>
       <c r="P92">
-        <v>-374.2721730000001</v>
+        <v>-380.9857527000001</v>
       </c>
       <c r="Q92">
-        <v>-253.9721730000001</v>
+        <v>-260.6857527000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4104750750281975</v>
+        <v>0.4509945278091084</v>
       </c>
       <c r="T92">
-        <v>5.641407430114419</v>
+        <v>6.26823047790491</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.09514298310929412</v>
+        <v>0.09409745582237879</v>
       </c>
       <c r="W92">
-        <v>0.2133652845828284</v>
+        <v>0.2136118199170831</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3805719324371765</v>
+        <v>0.3763898232895152</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2349762636273653</v>
+        <v>0.2368762636273654</v>
       </c>
       <c r="C93">
-        <v>-2613.381490829093</v>
+        <v>-2659.00072119172</v>
       </c>
       <c r="D93">
-        <v>770.0605091709076</v>
+        <v>762.4032788082808</v>
       </c>
       <c r="E93">
-        <v>2871.142</v>
+        <v>2909.104</v>
       </c>
       <c r="F93">
-        <v>3454.542</v>
+        <v>3492.504</v>
       </c>
       <c r="G93">
         <v>71.09999999999999</v>
@@ -8913,37 +8913,37 @@
         <v>306.6</v>
       </c>
       <c r="M93">
-        <v>814.5810036000001</v>
+        <v>823.5324432000001</v>
       </c>
       <c r="N93">
-        <v>-507.9810036000002</v>
+        <v>-516.9324432000001</v>
       </c>
       <c r="O93">
-        <v>-126.9952509</v>
+        <v>-129.2331108</v>
       </c>
       <c r="P93">
-        <v>-380.9857527000001</v>
+        <v>-387.6993324000001</v>
       </c>
       <c r="Q93">
-        <v>-260.6857527000001</v>
+        <v>-267.3993324</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4509945278091084</v>
+        <v>0.501643843785247</v>
       </c>
       <c r="T93">
-        <v>6.26823047790491</v>
+        <v>7.051759287643026</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.09409745582237879</v>
+        <v>0.09307465738952685</v>
       </c>
       <c r="W93">
-        <v>0.2136118199170831</v>
+        <v>0.2138529957875496</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3763898232895152</v>
+        <v>0.3722986295581074</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2368762636273654</v>
+        <v>0.2387762636273653</v>
       </c>
       <c r="C94">
-        <v>-2659.00072119172</v>
+        <v>-2704.469168889002</v>
       </c>
       <c r="D94">
-        <v>762.4032788082808</v>
+        <v>754.8968311109987</v>
       </c>
       <c r="E94">
-        <v>2909.104</v>
+        <v>2947.066</v>
       </c>
       <c r="F94">
-        <v>3492.504</v>
+        <v>3530.466</v>
       </c>
       <c r="G94">
         <v>71.09999999999999</v>
@@ -8995,37 +8995,37 @@
         <v>306.6</v>
       </c>
       <c r="M94">
-        <v>823.5324432000001</v>
+        <v>832.4838828000001</v>
       </c>
       <c r="N94">
-        <v>-516.9324432000001</v>
+        <v>-525.8838828</v>
       </c>
       <c r="O94">
-        <v>-129.2331108</v>
+        <v>-131.4709707</v>
       </c>
       <c r="P94">
-        <v>-387.6993324000001</v>
+        <v>-394.4129121</v>
       </c>
       <c r="Q94">
-        <v>-267.3993324</v>
+        <v>-274.1129121</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.501643843785247</v>
+        <v>0.5667643928974251</v>
       </c>
       <c r="T94">
-        <v>7.051759287643026</v>
+        <v>8.05915347159203</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09307465738952685</v>
+        <v>0.09207385462189753</v>
       </c>
       <c r="W94">
-        <v>0.2138529957875496</v>
+        <v>0.2140889850801566</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3722986295581074</v>
+        <v>0.3682954184875902</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2387762636273653</v>
+        <v>0.2406762636273653</v>
       </c>
       <c r="C95">
-        <v>-2704.469168889002</v>
+        <v>-2749.791244212764</v>
       </c>
       <c r="D95">
-        <v>754.8968311109987</v>
+        <v>747.5367557872358</v>
       </c>
       <c r="E95">
-        <v>2947.066</v>
+        <v>2985.028</v>
       </c>
       <c r="F95">
-        <v>3530.466</v>
+        <v>3568.428</v>
       </c>
       <c r="G95">
         <v>71.09999999999999</v>
@@ -9077,37 +9077,37 @@
         <v>306.6</v>
       </c>
       <c r="M95">
-        <v>832.4838828000001</v>
+        <v>841.4353224000001</v>
       </c>
       <c r="N95">
-        <v>-525.8838828</v>
+        <v>-534.8353224000002</v>
       </c>
       <c r="O95">
-        <v>-131.4709707</v>
+        <v>-133.7088306000001</v>
       </c>
       <c r="P95">
-        <v>-394.4129121</v>
+        <v>-401.1264918000002</v>
       </c>
       <c r="Q95">
-        <v>-274.1129121</v>
+        <v>-280.8264918000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5667643928974251</v>
+        <v>0.6535917917136628</v>
       </c>
       <c r="T95">
-        <v>8.05915347159203</v>
+        <v>9.40234571685737</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09207385462189753</v>
+        <v>0.09109434553017522</v>
       </c>
       <c r="W95">
-        <v>0.2140889850801566</v>
+        <v>0.2143199533239847</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3682954184875902</v>
+        <v>0.3643773821207008</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2406762636273653</v>
+        <v>0.2425762636273653</v>
       </c>
       <c r="C96">
-        <v>-2749.791244212764</v>
+        <v>-2794.971187118142</v>
       </c>
       <c r="D96">
-        <v>747.5367557872358</v>
+        <v>740.3188128818587</v>
       </c>
       <c r="E96">
-        <v>2985.028</v>
+        <v>3022.99</v>
       </c>
       <c r="F96">
-        <v>3568.428</v>
+        <v>3606.39</v>
       </c>
       <c r="G96">
         <v>71.09999999999999</v>
@@ -9159,37 +9159,37 @@
         <v>306.6</v>
       </c>
       <c r="M96">
-        <v>841.4353224000001</v>
+        <v>850.3867620000001</v>
       </c>
       <c r="N96">
-        <v>-534.8353224000002</v>
+        <v>-543.7867620000002</v>
       </c>
       <c r="O96">
-        <v>-133.7088306000001</v>
+        <v>-135.9466905</v>
       </c>
       <c r="P96">
-        <v>-401.1264918000002</v>
+        <v>-407.8400715000001</v>
       </c>
       <c r="Q96">
-        <v>-280.8264918000002</v>
+        <v>-287.5400715000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6535917917136628</v>
+        <v>0.7751501500563956</v>
       </c>
       <c r="T96">
-        <v>9.40234571685737</v>
+        <v>11.28281486022885</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09109434553017522</v>
+        <v>0.09013545768248916</v>
       </c>
       <c r="W96">
-        <v>0.2143199533239847</v>
+        <v>0.214546059078469</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3643773821207008</v>
+        <v>0.3605418307299566</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2425762636273653</v>
+        <v>0.2444762636273654</v>
       </c>
       <c r="C97">
-        <v>-2794.971187118142</v>
+        <v>-2840.013075368476</v>
       </c>
       <c r="D97">
-        <v>740.3188128818587</v>
+        <v>733.238924631525</v>
       </c>
       <c r="E97">
-        <v>3022.99</v>
+        <v>3060.952000000001</v>
       </c>
       <c r="F97">
-        <v>3606.39</v>
+        <v>3644.352000000001</v>
       </c>
       <c r="G97">
         <v>71.09999999999999</v>
@@ -9241,37 +9241,37 @@
         <v>306.6</v>
       </c>
       <c r="M97">
-        <v>850.3867620000001</v>
+        <v>859.3382016000002</v>
       </c>
       <c r="N97">
-        <v>-543.7867620000002</v>
+        <v>-552.7382016000001</v>
       </c>
       <c r="O97">
-        <v>-135.9466905</v>
+        <v>-138.1845504</v>
       </c>
       <c r="P97">
-        <v>-407.8400715000001</v>
+        <v>-414.5536512000001</v>
       </c>
       <c r="Q97">
-        <v>-287.5400715000001</v>
+        <v>-294.2536512000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7751501500563956</v>
+        <v>0.9574876875704952</v>
       </c>
       <c r="T97">
-        <v>11.28281486022885</v>
+        <v>14.10351857528607</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09013545768248916</v>
+        <v>0.08919654666496322</v>
       </c>
       <c r="W97">
-        <v>0.214546059078469</v>
+        <v>0.2147674542964017</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3605418307299566</v>
+        <v>0.356786186659853</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2444762636273654</v>
+        <v>0.2463762636273653</v>
       </c>
       <c r="C98">
-        <v>-2840.013075368475</v>
+        <v>-2884.920832217292</v>
       </c>
       <c r="D98">
-        <v>733.2389246315255</v>
+        <v>726.2931677827083</v>
       </c>
       <c r="E98">
-        <v>3060.952</v>
+        <v>3098.914</v>
       </c>
       <c r="F98">
-        <v>3644.352</v>
+        <v>3682.314</v>
       </c>
       <c r="G98">
         <v>71.09999999999999</v>
@@ -9323,37 +9323,37 @@
         <v>306.6</v>
       </c>
       <c r="M98">
-        <v>859.3382016000002</v>
+        <v>868.2896412000001</v>
       </c>
       <c r="N98">
-        <v>-552.7382016000001</v>
+        <v>-561.6896412000001</v>
       </c>
       <c r="O98">
-        <v>-138.1845504</v>
+        <v>-140.4224103</v>
       </c>
       <c r="P98">
-        <v>-414.5536512000001</v>
+        <v>-421.2672309000001</v>
       </c>
       <c r="Q98">
-        <v>-294.2536512000001</v>
+        <v>-300.9672309000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9574876875704926</v>
+        <v>1.261383583427324</v>
       </c>
       <c r="T98">
-        <v>14.10351857528603</v>
+        <v>18.80469143371471</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08919654666496322</v>
+        <v>0.08827699463748938</v>
       </c>
       <c r="W98">
-        <v>0.2147674542964017</v>
+        <v>0.21498428466448</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.356786186659853</v>
+        <v>0.3531079785499576</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2463762636273653</v>
+        <v>0.2482762636273654</v>
       </c>
       <c r="C99">
-        <v>-2884.920832217292</v>
+        <v>-2929.698233657763</v>
       </c>
       <c r="D99">
-        <v>726.2931677827083</v>
+        <v>719.4777663422371</v>
       </c>
       <c r="E99">
-        <v>3098.914</v>
+        <v>3136.876</v>
       </c>
       <c r="F99">
-        <v>3682.314</v>
+        <v>3720.276</v>
       </c>
       <c r="G99">
         <v>71.09999999999999</v>
@@ -9405,37 +9405,37 @@
         <v>306.6</v>
       </c>
       <c r="M99">
-        <v>868.2896412000001</v>
+        <v>877.2410808000001</v>
       </c>
       <c r="N99">
-        <v>-561.6896412000001</v>
+        <v>-570.6410808000001</v>
       </c>
       <c r="O99">
-        <v>-140.4224103</v>
+        <v>-142.6602702</v>
       </c>
       <c r="P99">
-        <v>-421.2672309000001</v>
+        <v>-427.9808106</v>
       </c>
       <c r="Q99">
-        <v>-300.9672309000001</v>
+        <v>-307.6808106</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.261383583427324</v>
+        <v>1.869175375140985</v>
       </c>
       <c r="T99">
-        <v>18.80469143371471</v>
+        <v>28.20703715057206</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08827699463748938</v>
+        <v>0.08737620897792317</v>
       </c>
       <c r="W99">
-        <v>0.21498428466448</v>
+        <v>0.2151966899230057</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3531079785499576</v>
+        <v>0.3495048359116928</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2482762636273654</v>
+        <v>0.2501762636273653</v>
       </c>
       <c r="C100">
-        <v>-2929.698233657763</v>
+        <v>-2974.348915267789</v>
       </c>
       <c r="D100">
-        <v>719.4777663422371</v>
+        <v>712.789084732211</v>
       </c>
       <c r="E100">
-        <v>3136.876</v>
+        <v>3174.838</v>
       </c>
       <c r="F100">
-        <v>3720.276</v>
+        <v>3758.238</v>
       </c>
       <c r="G100">
         <v>71.09999999999999</v>
@@ -9487,37 +9487,37 @@
         <v>306.6</v>
       </c>
       <c r="M100">
-        <v>877.2410808000001</v>
+        <v>886.1925204000001</v>
       </c>
       <c r="N100">
-        <v>-570.6410808000001</v>
+        <v>-579.5925204000002</v>
       </c>
       <c r="O100">
-        <v>-142.6602702</v>
+        <v>-144.8981301000001</v>
       </c>
       <c r="P100">
-        <v>-427.9808106</v>
+        <v>-434.6943903000002</v>
       </c>
       <c r="Q100">
-        <v>-307.6808106</v>
+        <v>-314.3943903000002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.869175375140985</v>
+        <v>3.692550750281971</v>
       </c>
       <c r="T100">
-        <v>28.20703715057206</v>
+        <v>56.41407430114413</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08737620897792317</v>
+        <v>0.08649362100844919</v>
       </c>
       <c r="W100">
-        <v>0.2151966899230057</v>
+        <v>0.2154048041662077</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3495048359116928</v>
+        <v>0.3459744840337967</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2501762636273653</v>
-      </c>
-      <c r="C101">
-        <v>-2974.348915267789</v>
-      </c>
-      <c r="D101">
-        <v>712.789084732211</v>
-      </c>
-      <c r="E101">
-        <v>3174.838</v>
-      </c>
-      <c r="F101">
-        <v>3758.238</v>
-      </c>
-      <c r="G101">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="H101">
-        <v>3212.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>426.9</v>
-      </c>
-      <c r="K101">
-        <v>120.3</v>
-      </c>
-      <c r="L101">
-        <v>306.6</v>
-      </c>
-      <c r="M101">
-        <v>886.1925204000001</v>
-      </c>
-      <c r="N101">
-        <v>-579.5925204000002</v>
-      </c>
-      <c r="O101">
-        <v>-144.8981301000001</v>
-      </c>
-      <c r="P101">
-        <v>-434.6943903000002</v>
-      </c>
-      <c r="Q101">
-        <v>-314.3943903000002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.692550750281971</v>
-      </c>
-      <c r="T101">
-        <v>56.41407430114413</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08649362100844919</v>
-      </c>
-      <c r="W101">
-        <v>0.2154048041662077</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3459744840337967</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
